--- a/docs/KLTN_NHOM_14/10.SprintBacklog.xlsx
+++ b/docs/KLTN_NHOM_14/10.SprintBacklog.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATN\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\real-estate\docs\KLTN_NHOM_14\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB6B4153-D16B-48A5-BF10-91B56F6EAC89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A641F560-553D-4AD6-8559-3FFB8245C5C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{B648C98A-0483-4228-98EF-65FEF54600CC}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{B648C98A-0483-4228-98EF-65FEF54600CC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint 1" sheetId="1" r:id="rId1"/>
@@ -1048,7 +1048,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="165">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1338,110 +1338,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1458,9 +1355,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1479,18 +1373,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1503,6 +1387,112 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2294,15 +2284,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:strRef>
-              <c:f>'Sprint 2'!$D$212</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Ước tính</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>Ước tính 360</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
@@ -2322,85 +2304,85 @@
               <c:strCache>
                 <c:ptCount val="28"/>
                 <c:pt idx="1">
-                  <c:v>16-Thg4</c:v>
+                  <c:v>16-Apr</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>17-Thg4</c:v>
+                  <c:v>17-Apr</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>18-Thg4</c:v>
+                  <c:v>18-Apr</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>19-Thg4</c:v>
+                  <c:v>19-Apr</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>20-Thg4</c:v>
+                  <c:v>20-Apr</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>21-Thg4</c:v>
+                  <c:v>21-Apr</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>22-Thg4</c:v>
+                  <c:v>22-Apr</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>23-Thg4</c:v>
+                  <c:v>23-Apr</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>24-Thg4</c:v>
+                  <c:v>24-Apr</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>25-Thg4</c:v>
+                  <c:v>25-Apr</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>26-Thg4</c:v>
+                  <c:v>26-Apr</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>27-Thg4</c:v>
+                  <c:v>27-Apr</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>28-Thg4</c:v>
+                  <c:v>28-Apr</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>29-Thg4</c:v>
+                  <c:v>29-Apr</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>30-Thg4</c:v>
+                  <c:v>30-Apr</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>01-Thg5</c:v>
+                  <c:v>1-May</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>02-Thg5</c:v>
+                  <c:v>2-May</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>03-Thg5</c:v>
+                  <c:v>3-May</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>04-Thg5</c:v>
+                  <c:v>4-May</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>05-Thg5</c:v>
+                  <c:v>5-May</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>06-Thg5</c:v>
+                  <c:v>6-May</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>07-Thg5</c:v>
+                  <c:v>7-May</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>08-Thg5</c:v>
+                  <c:v>8-May</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>09-Thg5</c:v>
+                  <c:v>9-May</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>10-Thg5</c:v>
+                  <c:v>10-May</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>11-Thg5</c:v>
+                  <c:v>11-May</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>12-Thg5</c:v>
+                  <c:v>12-May</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2509,15 +2491,7 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:strRef>
-              <c:f>'Sprint 2'!$D$213</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Thực tế</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>Thực tế 370</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
@@ -2537,85 +2511,85 @@
               <c:strCache>
                 <c:ptCount val="28"/>
                 <c:pt idx="1">
-                  <c:v>16-Thg4</c:v>
+                  <c:v>16-Apr</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>17-Thg4</c:v>
+                  <c:v>17-Apr</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>18-Thg4</c:v>
+                  <c:v>18-Apr</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>19-Thg4</c:v>
+                  <c:v>19-Apr</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>20-Thg4</c:v>
+                  <c:v>20-Apr</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>21-Thg4</c:v>
+                  <c:v>21-Apr</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>22-Thg4</c:v>
+                  <c:v>22-Apr</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>23-Thg4</c:v>
+                  <c:v>23-Apr</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>24-Thg4</c:v>
+                  <c:v>24-Apr</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>25-Thg4</c:v>
+                  <c:v>25-Apr</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>26-Thg4</c:v>
+                  <c:v>26-Apr</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>27-Thg4</c:v>
+                  <c:v>27-Apr</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>28-Thg4</c:v>
+                  <c:v>28-Apr</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>29-Thg4</c:v>
+                  <c:v>29-Apr</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>30-Thg4</c:v>
+                  <c:v>30-Apr</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>01-Thg5</c:v>
+                  <c:v>1-May</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>02-Thg5</c:v>
+                  <c:v>2-May</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>03-Thg5</c:v>
+                  <c:v>3-May</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>04-Thg5</c:v>
+                  <c:v>4-May</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>05-Thg5</c:v>
+                  <c:v>5-May</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>06-Thg5</c:v>
+                  <c:v>6-May</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>07-Thg5</c:v>
+                  <c:v>7-May</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>08-Thg5</c:v>
+                  <c:v>8-May</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>09-Thg5</c:v>
+                  <c:v>9-May</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>10-Thg5</c:v>
+                  <c:v>10-May</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>11-Thg5</c:v>
+                  <c:v>11-May</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>12-Thg5</c:v>
+                  <c:v>12-May</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4426,20 +4400,20 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="108" t="s">
+      <c r="B1" s="149" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="149"/>
+      <c r="M1" s="149"/>
     </row>
     <row r="2" spans="1:31" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -4499,14 +4473,14 @@
       <c r="M4" s="4"/>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="B6" s="113" t="s">
+      <c r="B6" s="150" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="114"/>
-      <c r="D6" s="114"/>
-      <c r="E6" s="114"/>
-      <c r="F6" s="114"/>
-      <c r="G6" s="112"/>
+      <c r="C6" s="151"/>
+      <c r="D6" s="151"/>
+      <c r="E6" s="151"/>
+      <c r="F6" s="151"/>
+      <c r="G6" s="137"/>
     </row>
     <row r="7" spans="1:31" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5" t="s">
@@ -4518,11 +4492,11 @@
       <c r="D7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="115" t="s">
+      <c r="E7" s="152" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="116"/>
-      <c r="G7" s="117"/>
+      <c r="F7" s="153"/>
+      <c r="G7" s="154"/>
     </row>
     <row r="8" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B8" s="7">
@@ -4535,17 +4509,17 @@
         <f>SUM(SUM(D117,D114,D116,D132,D147,D162,D205,D206)/5+SUM(D161,D175,D190,D203)/3+SUM(D123,D128,D153,D158,D182,D187)/2+SUM(D199,D193,D177,D171,D165,D148,D141,D146,D135,D119,D118))</f>
         <v>71.233333333333334</v>
       </c>
-      <c r="E8" s="118">
+      <c r="E8" s="146">
         <f>SUM(SUM(E17,E19,E20,E35,E50,E65,E108,E109)/5+SUM(E26,E31,E56,E61,E85,E90)/2+SUM(E64,E78,E93,E106)/3+SUM(E21,E22,E38,E44,E49,E51,E68,E74,E80,E96,E102))</f>
         <v>68.333333333333343</v>
       </c>
-      <c r="F8" s="119"/>
-      <c r="G8" s="120"/>
+      <c r="F8" s="147"/>
+      <c r="G8" s="148"/>
       <c r="J8" s="13"/>
-      <c r="K8" s="123" t="s">
+      <c r="K8" s="143" t="s">
         <v>16</v>
       </c>
-      <c r="L8" s="124"/>
+      <c r="L8" s="144"/>
     </row>
     <row r="9" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B9" s="10">
@@ -4558,17 +4532,17 @@
         <f>SUM(SUM(D117,D114,D116,D132,D147,D162,D205,D206)/5+SUM(D161,D175,D190,D203)/3+SUM(D136,D166,D168,D194,D196)/2+SUM(D120,D125,D127,D133,D143,D150,D152,D157,D163,D173,D174,D179,D181,D186,D191,D201,D202))</f>
         <v>74.733333333333334</v>
       </c>
-      <c r="E9" s="118">
+      <c r="E9" s="146">
         <f>SUM(SUM(E17,E19,E20,E35,E50,E65,E108,E109)/5+SUM(E64,E78,E93,E106)/3+SUM(E39,E69,E71,E97,E99)/2+SUM(E23,E28,E30,E36,E46,E53,E55,E60,E66,E76,E77,E82,E84,E89,E94,E104,E105))</f>
         <v>71.333333333333343</v>
       </c>
-      <c r="F9" s="119"/>
-      <c r="G9" s="120"/>
+      <c r="F9" s="147"/>
+      <c r="G9" s="148"/>
       <c r="J9" s="14"/>
-      <c r="K9" s="123" t="s">
+      <c r="K9" s="143" t="s">
         <v>17</v>
       </c>
-      <c r="L9" s="124"/>
+      <c r="L9" s="144"/>
     </row>
     <row r="10" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B10" s="10">
@@ -4581,17 +4555,17 @@
         <f>SUM(SUM(D117,D114,D116,D132,D147,D162,D205,D206)/5+SUM(D121,D128,D153,D160,D166,D176,D182,D189,D204,D194)/2+SUM(D126,D134,D138,D140,D144,D149,D170,D178,D198))</f>
         <v>67.900000000000006</v>
       </c>
-      <c r="E10" s="118">
+      <c r="E10" s="146">
         <f>SUM(SUM(E17,E19,E20,E35,E50,E65,E108,E109)/5+SUM(E24,E31,E56,E63,E69,E79,E85,E92,E97,E107)/2+SUM(E29,E37,E41,E43,E47,E52,E73,E81,E101))</f>
         <v>64.5</v>
       </c>
-      <c r="F10" s="119"/>
-      <c r="G10" s="120"/>
+      <c r="F10" s="147"/>
+      <c r="G10" s="148"/>
       <c r="J10" s="15"/>
-      <c r="K10" s="123" t="s">
+      <c r="K10" s="143" t="s">
         <v>18</v>
       </c>
-      <c r="L10" s="124"/>
+      <c r="L10" s="144"/>
     </row>
     <row r="11" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B11" s="10">
@@ -4604,17 +4578,17 @@
         <f>SUM(SUM(D117,D114,D116,D132,D147,D162,D205,D206)/5+SUM(D121,D160,D176,D189,D204)/2+SUM(D115,D124,D130,D131,D137,D142,D154,D156,D159,D164,D167,D172,D183,D185,D188,D192,D195,D200))</f>
         <v>90.9</v>
       </c>
-      <c r="E11" s="118">
+      <c r="E11" s="146">
         <f>SUM(SUM(E17,E19,E20,E35,E50,E65,E108,E109)/5+SUM(E24,E63,E79,E92,E107)/2+SUM(E18,E27,E33,E34,E40,E45,E57,E59,E62,E67,E70,E75,E86,E88,E91,E95,E98,E103))</f>
         <v>84</v>
       </c>
-      <c r="F11" s="119"/>
-      <c r="G11" s="120"/>
+      <c r="F11" s="147"/>
+      <c r="G11" s="148"/>
       <c r="J11" s="16"/>
-      <c r="K11" s="123" t="s">
+      <c r="K11" s="143" t="s">
         <v>19</v>
       </c>
-      <c r="L11" s="124"/>
+      <c r="L11" s="144"/>
     </row>
     <row r="12" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B12" s="10">
@@ -4627,33 +4601,33 @@
         <f>SUM(SUM(D117,D114,D116,D132,D147,D162,D205,D206)/5+SUM(D161,D175,D190,D203)/3+SUM(D123,D136,D158,D168,D187,D196)/2+SUM(D122,D129,D139,D145,D151,D155,D169,D180,D184,D197))</f>
         <v>68.233333333333334</v>
       </c>
-      <c r="E12" s="118">
+      <c r="E12" s="146">
         <f>SUM(SUM(E17,E19,E20,E35,E50,E65,E108,E109)/5+SUM(E64,E78,E93,E106)/3+SUM(E26,E39,E61,E71,E90,E99)/2+SUM(E25,E32,E42,E48,E54,E58,E72,E83,E87,E100))</f>
         <v>73.833333333333343</v>
       </c>
-      <c r="F12" s="119"/>
-      <c r="G12" s="120"/>
+      <c r="F12" s="147"/>
+      <c r="G12" s="148"/>
       <c r="J12" s="17"/>
-      <c r="K12" s="125" t="s">
+      <c r="K12" s="145" t="s">
         <v>20</v>
       </c>
-      <c r="L12" s="125"/>
+      <c r="L12" s="145"/>
     </row>
     <row r="13" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B13" s="121" t="s">
+      <c r="B13" s="155" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="122"/>
+      <c r="C13" s="156"/>
       <c r="D13" s="12">
         <f>SUM(D8:D12)</f>
         <v>373</v>
       </c>
-      <c r="E13" s="121">
+      <c r="E13" s="155">
         <f>SUM(E8:G12)</f>
         <v>362</v>
       </c>
-      <c r="F13" s="122"/>
-      <c r="G13" s="122"/>
+      <c r="F13" s="156"/>
+      <c r="G13" s="156"/>
     </row>
     <row r="16" spans="1:31" ht="52.2" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
@@ -4776,10 +4750,10 @@
       </c>
     </row>
     <row r="17" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="109" t="s">
+      <c r="A17" s="134" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="110"/>
+      <c r="B17" s="135"/>
       <c r="C17" s="22" t="s">
         <v>25</v>
       </c>
@@ -4867,10 +4841,10 @@
       </c>
     </row>
     <row r="18" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="109" t="s">
+      <c r="A18" s="134" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="110"/>
+      <c r="B18" s="135"/>
       <c r="C18" s="27" t="s">
         <v>40</v>
       </c>
@@ -4958,10 +4932,10 @@
       </c>
     </row>
     <row r="19" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="109" t="s">
+      <c r="A19" s="134" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="110"/>
+      <c r="B19" s="135"/>
       <c r="C19" s="22" t="s">
         <v>25</v>
       </c>
@@ -5049,10 +5023,10 @@
       </c>
     </row>
     <row r="20" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="111" t="s">
+      <c r="A20" s="136" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="112"/>
+      <c r="B20" s="137"/>
       <c r="C20" s="27" t="s">
         <v>25</v>
       </c>
@@ -5140,7 +5114,7 @@
       </c>
     </row>
     <row r="21" spans="1:31" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="129" t="s">
+      <c r="A21" s="138" t="s">
         <v>29</v>
       </c>
       <c r="B21" s="33" t="s">
@@ -5233,7 +5207,7 @@
       </c>
     </row>
     <row r="22" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="130"/>
+      <c r="A22" s="139"/>
       <c r="B22" s="33" t="s">
         <v>30</v>
       </c>
@@ -5324,7 +5298,7 @@
       </c>
     </row>
     <row r="23" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="130"/>
+      <c r="A23" s="139"/>
       <c r="B23" s="33" t="s">
         <v>31</v>
       </c>
@@ -5415,7 +5389,7 @@
       </c>
     </row>
     <row r="24" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="130"/>
+      <c r="A24" s="139"/>
       <c r="B24" s="33" t="s">
         <v>49</v>
       </c>
@@ -5506,7 +5480,7 @@
       </c>
     </row>
     <row r="25" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="130"/>
+      <c r="A25" s="139"/>
       <c r="B25" s="33" t="s">
         <v>50</v>
       </c>
@@ -5597,7 +5571,7 @@
       </c>
     </row>
     <row r="26" spans="1:31" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="130"/>
+      <c r="A26" s="139"/>
       <c r="B26" s="33" t="s">
         <v>51</v>
       </c>
@@ -5688,7 +5662,7 @@
       </c>
     </row>
     <row r="27" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="130"/>
+      <c r="A27" s="139"/>
       <c r="B27" s="33" t="s">
         <v>52</v>
       </c>
@@ -5779,7 +5753,7 @@
       </c>
     </row>
     <row r="28" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="130"/>
+      <c r="A28" s="139"/>
       <c r="B28" s="33" t="s">
         <v>53</v>
       </c>
@@ -5870,7 +5844,7 @@
       </c>
     </row>
     <row r="29" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="130"/>
+      <c r="A29" s="139"/>
       <c r="B29" s="33" t="s">
         <v>54</v>
       </c>
@@ -5961,7 +5935,7 @@
       </c>
     </row>
     <row r="30" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="130"/>
+      <c r="A30" s="139"/>
       <c r="B30" s="33" t="s">
         <v>55</v>
       </c>
@@ -6052,7 +6026,7 @@
       </c>
     </row>
     <row r="31" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="130"/>
+      <c r="A31" s="139"/>
       <c r="B31" s="33" t="s">
         <v>56</v>
       </c>
@@ -6143,7 +6117,7 @@
       </c>
     </row>
     <row r="32" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="130"/>
+      <c r="A32" s="139"/>
       <c r="B32" s="33" t="s">
         <v>57</v>
       </c>
@@ -6234,7 +6208,7 @@
       </c>
     </row>
     <row r="33" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="130"/>
+      <c r="A33" s="139"/>
       <c r="B33" s="33" t="s">
         <v>58</v>
       </c>
@@ -6325,7 +6299,7 @@
       </c>
     </row>
     <row r="34" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="130"/>
+      <c r="A34" s="139"/>
       <c r="B34" s="33" t="s">
         <v>59</v>
       </c>
@@ -6416,7 +6390,7 @@
       </c>
     </row>
     <row r="35" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="131"/>
+      <c r="A35" s="140"/>
       <c r="B35" s="33" t="s">
         <v>32</v>
       </c>
@@ -6507,7 +6481,7 @@
       </c>
     </row>
     <row r="36" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="132" t="s">
+      <c r="A36" s="141" t="s">
         <v>33</v>
       </c>
       <c r="B36" s="33" t="s">
@@ -6600,7 +6574,7 @@
       </c>
     </row>
     <row r="37" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="133"/>
+      <c r="A37" s="142"/>
       <c r="B37" s="33" t="s">
         <v>30</v>
       </c>
@@ -6691,7 +6665,7 @@
       </c>
     </row>
     <row r="38" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A38" s="133"/>
+      <c r="A38" s="142"/>
       <c r="B38" s="33" t="s">
         <v>31</v>
       </c>
@@ -6782,7 +6756,7 @@
       </c>
     </row>
     <row r="39" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A39" s="133"/>
+      <c r="A39" s="142"/>
       <c r="B39" s="33" t="s">
         <v>49</v>
       </c>
@@ -6873,7 +6847,7 @@
       </c>
     </row>
     <row r="40" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A40" s="133"/>
+      <c r="A40" s="142"/>
       <c r="B40" s="33" t="s">
         <v>50</v>
       </c>
@@ -6964,7 +6938,7 @@
       </c>
     </row>
     <row r="41" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A41" s="133"/>
+      <c r="A41" s="142"/>
       <c r="B41" s="33" t="s">
         <v>51</v>
       </c>
@@ -7055,7 +7029,7 @@
       </c>
     </row>
     <row r="42" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A42" s="133"/>
+      <c r="A42" s="142"/>
       <c r="B42" s="33" t="s">
         <v>52</v>
       </c>
@@ -7146,7 +7120,7 @@
       </c>
     </row>
     <row r="43" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A43" s="133"/>
+      <c r="A43" s="142"/>
       <c r="B43" s="33" t="s">
         <v>53</v>
       </c>
@@ -7237,7 +7211,7 @@
       </c>
     </row>
     <row r="44" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A44" s="133"/>
+      <c r="A44" s="142"/>
       <c r="B44" s="33" t="s">
         <v>54</v>
       </c>
@@ -7328,7 +7302,7 @@
       </c>
     </row>
     <row r="45" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A45" s="133"/>
+      <c r="A45" s="142"/>
       <c r="B45" s="33" t="s">
         <v>55</v>
       </c>
@@ -7419,7 +7393,7 @@
       </c>
     </row>
     <row r="46" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A46" s="133"/>
+      <c r="A46" s="142"/>
       <c r="B46" s="33" t="s">
         <v>56</v>
       </c>
@@ -7510,7 +7484,7 @@
       </c>
     </row>
     <row r="47" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A47" s="133"/>
+      <c r="A47" s="142"/>
       <c r="B47" s="33" t="s">
         <v>57</v>
       </c>
@@ -7601,7 +7575,7 @@
       </c>
     </row>
     <row r="48" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A48" s="133"/>
+      <c r="A48" s="142"/>
       <c r="B48" s="33" t="s">
         <v>58</v>
       </c>
@@ -7692,7 +7666,7 @@
       </c>
     </row>
     <row r="49" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A49" s="133"/>
+      <c r="A49" s="142"/>
       <c r="B49" s="33" t="s">
         <v>59</v>
       </c>
@@ -7783,7 +7757,7 @@
       </c>
     </row>
     <row r="50" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="133"/>
+      <c r="A50" s="142"/>
       <c r="B50" s="33" t="s">
         <v>32</v>
       </c>
@@ -7874,7 +7848,7 @@
       </c>
     </row>
     <row r="51" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A51" s="134" t="s">
+      <c r="A51" s="130" t="s">
         <v>34</v>
       </c>
       <c r="B51" s="33" t="s">
@@ -7967,7 +7941,7 @@
       </c>
     </row>
     <row r="52" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A52" s="134"/>
+      <c r="A52" s="130"/>
       <c r="B52" s="33" t="s">
         <v>30</v>
       </c>
@@ -8058,7 +8032,7 @@
       </c>
     </row>
     <row r="53" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A53" s="134"/>
+      <c r="A53" s="130"/>
       <c r="B53" s="33" t="s">
         <v>31</v>
       </c>
@@ -8149,7 +8123,7 @@
       </c>
     </row>
     <row r="54" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A54" s="134"/>
+      <c r="A54" s="130"/>
       <c r="B54" s="33" t="s">
         <v>49</v>
       </c>
@@ -8240,7 +8214,7 @@
       </c>
     </row>
     <row r="55" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A55" s="134"/>
+      <c r="A55" s="130"/>
       <c r="B55" s="33" t="s">
         <v>50</v>
       </c>
@@ -8331,7 +8305,7 @@
       </c>
     </row>
     <row r="56" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="134"/>
+      <c r="A56" s="130"/>
       <c r="B56" s="33" t="s">
         <v>51</v>
       </c>
@@ -8422,7 +8396,7 @@
       </c>
     </row>
     <row r="57" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A57" s="134"/>
+      <c r="A57" s="130"/>
       <c r="B57" s="33" t="s">
         <v>52</v>
       </c>
@@ -8513,7 +8487,7 @@
       </c>
     </row>
     <row r="58" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A58" s="134"/>
+      <c r="A58" s="130"/>
       <c r="B58" s="33" t="s">
         <v>53</v>
       </c>
@@ -8604,7 +8578,7 @@
       </c>
     </row>
     <row r="59" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A59" s="134"/>
+      <c r="A59" s="130"/>
       <c r="B59" s="33" t="s">
         <v>54</v>
       </c>
@@ -8695,7 +8669,7 @@
       </c>
     </row>
     <row r="60" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A60" s="134"/>
+      <c r="A60" s="130"/>
       <c r="B60" s="33" t="s">
         <v>55</v>
       </c>
@@ -8786,7 +8760,7 @@
       </c>
     </row>
     <row r="61" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A61" s="134"/>
+      <c r="A61" s="130"/>
       <c r="B61" s="33" t="s">
         <v>56</v>
       </c>
@@ -8877,7 +8851,7 @@
       </c>
     </row>
     <row r="62" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A62" s="134"/>
+      <c r="A62" s="130"/>
       <c r="B62" s="33" t="s">
         <v>57</v>
       </c>
@@ -8968,7 +8942,7 @@
       </c>
     </row>
     <row r="63" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A63" s="134"/>
+      <c r="A63" s="130"/>
       <c r="B63" s="33" t="s">
         <v>58</v>
       </c>
@@ -9059,7 +9033,7 @@
       </c>
     </row>
     <row r="64" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A64" s="134"/>
+      <c r="A64" s="130"/>
       <c r="B64" s="33" t="s">
         <v>59</v>
       </c>
@@ -9150,7 +9124,7 @@
       </c>
     </row>
     <row r="65" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A65" s="134"/>
+      <c r="A65" s="130"/>
       <c r="B65" s="33" t="s">
         <v>65</v>
       </c>
@@ -9241,7 +9215,7 @@
       </c>
     </row>
     <row r="66" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A66" s="134" t="s">
+      <c r="A66" s="130" t="s">
         <v>35</v>
       </c>
       <c r="B66" s="33" t="s">
@@ -9334,7 +9308,7 @@
       </c>
     </row>
     <row r="67" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A67" s="134"/>
+      <c r="A67" s="130"/>
       <c r="B67" s="33" t="s">
         <v>30</v>
       </c>
@@ -9425,7 +9399,7 @@
       </c>
     </row>
     <row r="68" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A68" s="134"/>
+      <c r="A68" s="130"/>
       <c r="B68" s="33" t="s">
         <v>31</v>
       </c>
@@ -9516,7 +9490,7 @@
       </c>
     </row>
     <row r="69" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A69" s="134"/>
+      <c r="A69" s="130"/>
       <c r="B69" s="33" t="s">
         <v>49</v>
       </c>
@@ -9607,7 +9581,7 @@
       </c>
     </row>
     <row r="70" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A70" s="134"/>
+      <c r="A70" s="130"/>
       <c r="B70" s="33" t="s">
         <v>50</v>
       </c>
@@ -9698,7 +9672,7 @@
       </c>
     </row>
     <row r="71" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A71" s="134"/>
+      <c r="A71" s="130"/>
       <c r="B71" s="33" t="s">
         <v>51</v>
       </c>
@@ -9789,7 +9763,7 @@
       </c>
     </row>
     <row r="72" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A72" s="134"/>
+      <c r="A72" s="130"/>
       <c r="B72" s="33" t="s">
         <v>52</v>
       </c>
@@ -9880,7 +9854,7 @@
       </c>
     </row>
     <row r="73" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A73" s="134"/>
+      <c r="A73" s="130"/>
       <c r="B73" s="33" t="s">
         <v>53</v>
       </c>
@@ -9971,7 +9945,7 @@
       </c>
     </row>
     <row r="74" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A74" s="134"/>
+      <c r="A74" s="130"/>
       <c r="B74" s="33" t="s">
         <v>54</v>
       </c>
@@ -10062,7 +10036,7 @@
       </c>
     </row>
     <row r="75" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A75" s="134"/>
+      <c r="A75" s="130"/>
       <c r="B75" s="33" t="s">
         <v>55</v>
       </c>
@@ -10153,7 +10127,7 @@
       </c>
     </row>
     <row r="76" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A76" s="134"/>
+      <c r="A76" s="130"/>
       <c r="B76" s="33" t="s">
         <v>56</v>
       </c>
@@ -10244,7 +10218,7 @@
       </c>
     </row>
     <row r="77" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A77" s="134"/>
+      <c r="A77" s="130"/>
       <c r="B77" s="33" t="s">
         <v>57</v>
       </c>
@@ -10335,7 +10309,7 @@
       </c>
     </row>
     <row r="78" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A78" s="134"/>
+      <c r="A78" s="130"/>
       <c r="B78" s="33" t="s">
         <v>58</v>
       </c>
@@ -10426,7 +10400,7 @@
       </c>
     </row>
     <row r="79" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A79" s="134"/>
+      <c r="A79" s="130"/>
       <c r="B79" s="33" t="s">
         <v>59</v>
       </c>
@@ -10514,7 +10488,7 @@
       </c>
     </row>
     <row r="80" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A80" s="134" t="s">
+      <c r="A80" s="130" t="s">
         <v>36</v>
       </c>
       <c r="B80" s="33" t="s">
@@ -10607,7 +10581,7 @@
       </c>
     </row>
     <row r="81" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A81" s="134"/>
+      <c r="A81" s="130"/>
       <c r="B81" s="33" t="s">
         <v>30</v>
       </c>
@@ -10698,7 +10672,7 @@
       </c>
     </row>
     <row r="82" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A82" s="134"/>
+      <c r="A82" s="130"/>
       <c r="B82" s="33" t="s">
         <v>31</v>
       </c>
@@ -10789,7 +10763,7 @@
       </c>
     </row>
     <row r="83" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A83" s="134"/>
+      <c r="A83" s="130"/>
       <c r="B83" s="33" t="s">
         <v>49</v>
       </c>
@@ -10880,7 +10854,7 @@
       </c>
     </row>
     <row r="84" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A84" s="134"/>
+      <c r="A84" s="130"/>
       <c r="B84" s="33" t="s">
         <v>50</v>
       </c>
@@ -10971,7 +10945,7 @@
       </c>
     </row>
     <row r="85" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A85" s="134"/>
+      <c r="A85" s="130"/>
       <c r="B85" s="33" t="s">
         <v>51</v>
       </c>
@@ -11062,7 +11036,7 @@
       </c>
     </row>
     <row r="86" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A86" s="134"/>
+      <c r="A86" s="130"/>
       <c r="B86" s="33" t="s">
         <v>52</v>
       </c>
@@ -11153,7 +11127,7 @@
       </c>
     </row>
     <row r="87" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A87" s="134"/>
+      <c r="A87" s="130"/>
       <c r="B87" s="33" t="s">
         <v>53</v>
       </c>
@@ -11244,7 +11218,7 @@
       </c>
     </row>
     <row r="88" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A88" s="134"/>
+      <c r="A88" s="130"/>
       <c r="B88" s="33" t="s">
         <v>54</v>
       </c>
@@ -11335,7 +11309,7 @@
       </c>
     </row>
     <row r="89" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A89" s="134"/>
+      <c r="A89" s="130"/>
       <c r="B89" s="33" t="s">
         <v>55</v>
       </c>
@@ -11426,7 +11400,7 @@
       </c>
     </row>
     <row r="90" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A90" s="134"/>
+      <c r="A90" s="130"/>
       <c r="B90" s="33" t="s">
         <v>56</v>
       </c>
@@ -11517,7 +11491,7 @@
       </c>
     </row>
     <row r="91" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A91" s="134"/>
+      <c r="A91" s="130"/>
       <c r="B91" s="33" t="s">
         <v>57</v>
       </c>
@@ -11608,7 +11582,7 @@
       </c>
     </row>
     <row r="92" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A92" s="134"/>
+      <c r="A92" s="130"/>
       <c r="B92" s="33" t="s">
         <v>58</v>
       </c>
@@ -11699,7 +11673,7 @@
       </c>
     </row>
     <row r="93" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A93" s="134"/>
+      <c r="A93" s="130"/>
       <c r="B93" s="33" t="s">
         <v>59</v>
       </c>
@@ -11790,7 +11764,7 @@
       </c>
     </row>
     <row r="94" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A94" s="134" t="s">
+      <c r="A94" s="130" t="s">
         <v>37</v>
       </c>
       <c r="B94" s="33" t="s">
@@ -11883,7 +11857,7 @@
       </c>
     </row>
     <row r="95" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A95" s="134"/>
+      <c r="A95" s="130"/>
       <c r="B95" s="33" t="s">
         <v>30</v>
       </c>
@@ -11974,7 +11948,7 @@
       </c>
     </row>
     <row r="96" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A96" s="134"/>
+      <c r="A96" s="130"/>
       <c r="B96" s="33" t="s">
         <v>31</v>
       </c>
@@ -12065,7 +12039,7 @@
       </c>
     </row>
     <row r="97" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A97" s="134"/>
+      <c r="A97" s="130"/>
       <c r="B97" s="33" t="s">
         <v>49</v>
       </c>
@@ -12156,7 +12130,7 @@
       </c>
     </row>
     <row r="98" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A98" s="134"/>
+      <c r="A98" s="130"/>
       <c r="B98" s="33" t="s">
         <v>50</v>
       </c>
@@ -12244,7 +12218,7 @@
       </c>
     </row>
     <row r="99" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A99" s="134"/>
+      <c r="A99" s="130"/>
       <c r="B99" s="33" t="s">
         <v>51</v>
       </c>
@@ -12335,7 +12309,7 @@
       </c>
     </row>
     <row r="100" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A100" s="134"/>
+      <c r="A100" s="130"/>
       <c r="B100" s="33" t="s">
         <v>52</v>
       </c>
@@ -12426,7 +12400,7 @@
       </c>
     </row>
     <row r="101" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A101" s="134"/>
+      <c r="A101" s="130"/>
       <c r="B101" s="33" t="s">
         <v>53</v>
       </c>
@@ -12517,7 +12491,7 @@
       </c>
     </row>
     <row r="102" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A102" s="134"/>
+      <c r="A102" s="130"/>
       <c r="B102" s="33" t="s">
         <v>54</v>
       </c>
@@ -12608,7 +12582,7 @@
       </c>
     </row>
     <row r="103" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A103" s="134"/>
+      <c r="A103" s="130"/>
       <c r="B103" s="33" t="s">
         <v>55</v>
       </c>
@@ -12699,7 +12673,7 @@
       </c>
     </row>
     <row r="104" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A104" s="134"/>
+      <c r="A104" s="130"/>
       <c r="B104" s="33" t="s">
         <v>56</v>
       </c>
@@ -12790,7 +12764,7 @@
       </c>
     </row>
     <row r="105" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A105" s="134"/>
+      <c r="A105" s="130"/>
       <c r="B105" s="33" t="s">
         <v>57</v>
       </c>
@@ -12881,7 +12855,7 @@
       </c>
     </row>
     <row r="106" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A106" s="134"/>
+      <c r="A106" s="130"/>
       <c r="B106" s="33" t="s">
         <v>58</v>
       </c>
@@ -12972,7 +12946,7 @@
       </c>
     </row>
     <row r="107" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A107" s="134"/>
+      <c r="A107" s="130"/>
       <c r="B107" s="33" t="s">
         <v>59</v>
       </c>
@@ -13063,10 +13037,10 @@
       </c>
     </row>
     <row r="108" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A108" s="135" t="s">
+      <c r="A108" s="131" t="s">
         <v>38</v>
       </c>
-      <c r="B108" s="135"/>
+      <c r="B108" s="131"/>
       <c r="C108" s="44" t="s">
         <v>25</v>
       </c>
@@ -13154,10 +13128,10 @@
       </c>
     </row>
     <row r="109" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A109" s="136" t="s">
+      <c r="A109" s="132" t="s">
         <v>39</v>
       </c>
-      <c r="B109" s="137"/>
+      <c r="B109" s="133"/>
       <c r="C109" s="47" t="s">
         <v>25</v>
       </c>
@@ -13481,10 +13455,10 @@
       </c>
     </row>
     <row r="114" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A114" s="109" t="s">
+      <c r="A114" s="134" t="s">
         <v>24</v>
       </c>
-      <c r="B114" s="110"/>
+      <c r="B114" s="135"/>
       <c r="C114" s="22" t="s">
         <v>25</v>
       </c>
@@ -13572,10 +13546,10 @@
       </c>
     </row>
     <row r="115" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A115" s="109" t="s">
+      <c r="A115" s="134" t="s">
         <v>26</v>
       </c>
-      <c r="B115" s="110"/>
+      <c r="B115" s="135"/>
       <c r="C115" s="27" t="s">
         <v>40</v>
       </c>
@@ -13663,10 +13637,10 @@
       </c>
     </row>
     <row r="116" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A116" s="109" t="s">
+      <c r="A116" s="134" t="s">
         <v>27</v>
       </c>
-      <c r="B116" s="110"/>
+      <c r="B116" s="135"/>
       <c r="C116" s="22" t="s">
         <v>25</v>
       </c>
@@ -13754,10 +13728,10 @@
       </c>
     </row>
     <row r="117" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A117" s="111" t="s">
+      <c r="A117" s="136" t="s">
         <v>28</v>
       </c>
-      <c r="B117" s="112"/>
+      <c r="B117" s="137"/>
       <c r="C117" s="27" t="s">
         <v>25</v>
       </c>
@@ -13845,7 +13819,7 @@
       </c>
     </row>
     <row r="118" spans="1:31" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="129" t="s">
+      <c r="A118" s="138" t="s">
         <v>29</v>
       </c>
       <c r="B118" s="33" t="s">
@@ -13938,7 +13912,7 @@
       </c>
     </row>
     <row r="119" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A119" s="130"/>
+      <c r="A119" s="139"/>
       <c r="B119" s="33" t="s">
         <v>30</v>
       </c>
@@ -14029,7 +14003,7 @@
       </c>
     </row>
     <row r="120" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A120" s="130"/>
+      <c r="A120" s="139"/>
       <c r="B120" s="33" t="s">
         <v>31</v>
       </c>
@@ -14120,7 +14094,7 @@
       </c>
     </row>
     <row r="121" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A121" s="130"/>
+      <c r="A121" s="139"/>
       <c r="B121" s="33" t="s">
         <v>49</v>
       </c>
@@ -14211,7 +14185,7 @@
       </c>
     </row>
     <row r="122" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A122" s="130"/>
+      <c r="A122" s="139"/>
       <c r="B122" s="33" t="s">
         <v>50</v>
       </c>
@@ -14302,7 +14276,7 @@
       </c>
     </row>
     <row r="123" spans="1:31" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="130"/>
+      <c r="A123" s="139"/>
       <c r="B123" s="33" t="s">
         <v>51</v>
       </c>
@@ -14393,7 +14367,7 @@
       </c>
     </row>
     <row r="124" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A124" s="130"/>
+      <c r="A124" s="139"/>
       <c r="B124" s="33" t="s">
         <v>52</v>
       </c>
@@ -14484,7 +14458,7 @@
       </c>
     </row>
     <row r="125" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A125" s="130"/>
+      <c r="A125" s="139"/>
       <c r="B125" s="33" t="s">
         <v>53</v>
       </c>
@@ -14575,7 +14549,7 @@
       </c>
     </row>
     <row r="126" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A126" s="130"/>
+      <c r="A126" s="139"/>
       <c r="B126" s="33" t="s">
         <v>54</v>
       </c>
@@ -14666,7 +14640,7 @@
       </c>
     </row>
     <row r="127" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A127" s="130"/>
+      <c r="A127" s="139"/>
       <c r="B127" s="33" t="s">
         <v>55</v>
       </c>
@@ -14757,7 +14731,7 @@
       </c>
     </row>
     <row r="128" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A128" s="130"/>
+      <c r="A128" s="139"/>
       <c r="B128" s="33" t="s">
         <v>56</v>
       </c>
@@ -14848,7 +14822,7 @@
       </c>
     </row>
     <row r="129" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A129" s="130"/>
+      <c r="A129" s="139"/>
       <c r="B129" s="33" t="s">
         <v>57</v>
       </c>
@@ -14939,7 +14913,7 @@
       </c>
     </row>
     <row r="130" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A130" s="130"/>
+      <c r="A130" s="139"/>
       <c r="B130" s="33" t="s">
         <v>58</v>
       </c>
@@ -15030,7 +15004,7 @@
       </c>
     </row>
     <row r="131" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A131" s="130"/>
+      <c r="A131" s="139"/>
       <c r="B131" s="33" t="s">
         <v>59</v>
       </c>
@@ -15121,7 +15095,7 @@
       </c>
     </row>
     <row r="132" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A132" s="131"/>
+      <c r="A132" s="140"/>
       <c r="B132" s="33" t="s">
         <v>32</v>
       </c>
@@ -15212,7 +15186,7 @@
       </c>
     </row>
     <row r="133" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A133" s="132" t="s">
+      <c r="A133" s="141" t="s">
         <v>33</v>
       </c>
       <c r="B133" s="33" t="s">
@@ -15305,7 +15279,7 @@
       </c>
     </row>
     <row r="134" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A134" s="133"/>
+      <c r="A134" s="142"/>
       <c r="B134" s="33" t="s">
         <v>30</v>
       </c>
@@ -15396,7 +15370,7 @@
       </c>
     </row>
     <row r="135" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A135" s="133"/>
+      <c r="A135" s="142"/>
       <c r="B135" s="33" t="s">
         <v>31</v>
       </c>
@@ -15487,7 +15461,7 @@
       </c>
     </row>
     <row r="136" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A136" s="133"/>
+      <c r="A136" s="142"/>
       <c r="B136" s="33" t="s">
         <v>49</v>
       </c>
@@ -15578,7 +15552,7 @@
       </c>
     </row>
     <row r="137" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A137" s="133"/>
+      <c r="A137" s="142"/>
       <c r="B137" s="33" t="s">
         <v>50</v>
       </c>
@@ -15669,7 +15643,7 @@
       </c>
     </row>
     <row r="138" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A138" s="133"/>
+      <c r="A138" s="142"/>
       <c r="B138" s="33" t="s">
         <v>51</v>
       </c>
@@ -15760,7 +15734,7 @@
       </c>
     </row>
     <row r="139" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A139" s="133"/>
+      <c r="A139" s="142"/>
       <c r="B139" s="33" t="s">
         <v>52</v>
       </c>
@@ -15851,7 +15825,7 @@
       </c>
     </row>
     <row r="140" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A140" s="133"/>
+      <c r="A140" s="142"/>
       <c r="B140" s="33" t="s">
         <v>53</v>
       </c>
@@ -15942,7 +15916,7 @@
       </c>
     </row>
     <row r="141" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A141" s="133"/>
+      <c r="A141" s="142"/>
       <c r="B141" s="33" t="s">
         <v>54</v>
       </c>
@@ -16033,7 +16007,7 @@
       </c>
     </row>
     <row r="142" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A142" s="133"/>
+      <c r="A142" s="142"/>
       <c r="B142" s="33" t="s">
         <v>55</v>
       </c>
@@ -16124,7 +16098,7 @@
       </c>
     </row>
     <row r="143" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A143" s="133"/>
+      <c r="A143" s="142"/>
       <c r="B143" s="33" t="s">
         <v>56</v>
       </c>
@@ -16215,7 +16189,7 @@
       </c>
     </row>
     <row r="144" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A144" s="133"/>
+      <c r="A144" s="142"/>
       <c r="B144" s="33" t="s">
         <v>57</v>
       </c>
@@ -16306,7 +16280,7 @@
       </c>
     </row>
     <row r="145" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A145" s="133"/>
+      <c r="A145" s="142"/>
       <c r="B145" s="33" t="s">
         <v>58</v>
       </c>
@@ -16397,7 +16371,7 @@
       </c>
     </row>
     <row r="146" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A146" s="133"/>
+      <c r="A146" s="142"/>
       <c r="B146" s="33" t="s">
         <v>59</v>
       </c>
@@ -16488,7 +16462,7 @@
       </c>
     </row>
     <row r="147" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A147" s="133"/>
+      <c r="A147" s="142"/>
       <c r="B147" s="33" t="s">
         <v>32</v>
       </c>
@@ -16579,7 +16553,7 @@
       </c>
     </row>
     <row r="148" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A148" s="134" t="s">
+      <c r="A148" s="130" t="s">
         <v>34</v>
       </c>
       <c r="B148" s="33" t="s">
@@ -16672,7 +16646,7 @@
       </c>
     </row>
     <row r="149" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A149" s="134"/>
+      <c r="A149" s="130"/>
       <c r="B149" s="33" t="s">
         <v>30</v>
       </c>
@@ -16763,7 +16737,7 @@
       </c>
     </row>
     <row r="150" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A150" s="134"/>
+      <c r="A150" s="130"/>
       <c r="B150" s="33" t="s">
         <v>31</v>
       </c>
@@ -16854,7 +16828,7 @@
       </c>
     </row>
     <row r="151" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A151" s="134"/>
+      <c r="A151" s="130"/>
       <c r="B151" s="33" t="s">
         <v>49</v>
       </c>
@@ -16945,7 +16919,7 @@
       </c>
     </row>
     <row r="152" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A152" s="134"/>
+      <c r="A152" s="130"/>
       <c r="B152" s="33" t="s">
         <v>50</v>
       </c>
@@ -17036,7 +17010,7 @@
       </c>
     </row>
     <row r="153" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A153" s="134"/>
+      <c r="A153" s="130"/>
       <c r="B153" s="33" t="s">
         <v>51</v>
       </c>
@@ -17127,7 +17101,7 @@
       </c>
     </row>
     <row r="154" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A154" s="134"/>
+      <c r="A154" s="130"/>
       <c r="B154" s="33" t="s">
         <v>52</v>
       </c>
@@ -17218,7 +17192,7 @@
       </c>
     </row>
     <row r="155" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A155" s="134"/>
+      <c r="A155" s="130"/>
       <c r="B155" s="33" t="s">
         <v>53</v>
       </c>
@@ -17309,7 +17283,7 @@
       </c>
     </row>
     <row r="156" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A156" s="134"/>
+      <c r="A156" s="130"/>
       <c r="B156" s="33" t="s">
         <v>54</v>
       </c>
@@ -17400,7 +17374,7 @@
       </c>
     </row>
     <row r="157" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A157" s="134"/>
+      <c r="A157" s="130"/>
       <c r="B157" s="33" t="s">
         <v>55</v>
       </c>
@@ -17491,7 +17465,7 @@
       </c>
     </row>
     <row r="158" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A158" s="134"/>
+      <c r="A158" s="130"/>
       <c r="B158" s="33" t="s">
         <v>56</v>
       </c>
@@ -17582,7 +17556,7 @@
       </c>
     </row>
     <row r="159" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A159" s="134"/>
+      <c r="A159" s="130"/>
       <c r="B159" s="33" t="s">
         <v>57</v>
       </c>
@@ -17673,7 +17647,7 @@
       </c>
     </row>
     <row r="160" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A160" s="134"/>
+      <c r="A160" s="130"/>
       <c r="B160" s="33" t="s">
         <v>58</v>
       </c>
@@ -17764,7 +17738,7 @@
       </c>
     </row>
     <row r="161" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A161" s="134"/>
+      <c r="A161" s="130"/>
       <c r="B161" s="33" t="s">
         <v>59</v>
       </c>
@@ -17855,7 +17829,7 @@
       </c>
     </row>
     <row r="162" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A162" s="134"/>
+      <c r="A162" s="130"/>
       <c r="B162" s="33" t="s">
         <v>65</v>
       </c>
@@ -17946,7 +17920,7 @@
       </c>
     </row>
     <row r="163" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A163" s="134" t="s">
+      <c r="A163" s="130" t="s">
         <v>35</v>
       </c>
       <c r="B163" s="33" t="s">
@@ -18039,7 +18013,7 @@
       </c>
     </row>
     <row r="164" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A164" s="134"/>
+      <c r="A164" s="130"/>
       <c r="B164" s="33" t="s">
         <v>30</v>
       </c>
@@ -18130,7 +18104,7 @@
       </c>
     </row>
     <row r="165" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A165" s="134"/>
+      <c r="A165" s="130"/>
       <c r="B165" s="33" t="s">
         <v>31</v>
       </c>
@@ -18221,7 +18195,7 @@
       </c>
     </row>
     <row r="166" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A166" s="134"/>
+      <c r="A166" s="130"/>
       <c r="B166" s="33" t="s">
         <v>49</v>
       </c>
@@ -18312,7 +18286,7 @@
       </c>
     </row>
     <row r="167" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A167" s="134"/>
+      <c r="A167" s="130"/>
       <c r="B167" s="33" t="s">
         <v>50</v>
       </c>
@@ -18403,7 +18377,7 @@
       </c>
     </row>
     <row r="168" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A168" s="134"/>
+      <c r="A168" s="130"/>
       <c r="B168" s="33" t="s">
         <v>51</v>
       </c>
@@ -18494,7 +18468,7 @@
       </c>
     </row>
     <row r="169" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A169" s="134"/>
+      <c r="A169" s="130"/>
       <c r="B169" s="33" t="s">
         <v>52</v>
       </c>
@@ -18585,7 +18559,7 @@
       </c>
     </row>
     <row r="170" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A170" s="134"/>
+      <c r="A170" s="130"/>
       <c r="B170" s="33" t="s">
         <v>53</v>
       </c>
@@ -18676,7 +18650,7 @@
       </c>
     </row>
     <row r="171" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A171" s="134"/>
+      <c r="A171" s="130"/>
       <c r="B171" s="33" t="s">
         <v>54</v>
       </c>
@@ -18767,7 +18741,7 @@
       </c>
     </row>
     <row r="172" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A172" s="134"/>
+      <c r="A172" s="130"/>
       <c r="B172" s="33" t="s">
         <v>55</v>
       </c>
@@ -18858,7 +18832,7 @@
       </c>
     </row>
     <row r="173" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A173" s="134"/>
+      <c r="A173" s="130"/>
       <c r="B173" s="33" t="s">
         <v>56</v>
       </c>
@@ -18949,7 +18923,7 @@
       </c>
     </row>
     <row r="174" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A174" s="134"/>
+      <c r="A174" s="130"/>
       <c r="B174" s="33" t="s">
         <v>57</v>
       </c>
@@ -19040,7 +19014,7 @@
       </c>
     </row>
     <row r="175" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A175" s="134"/>
+      <c r="A175" s="130"/>
       <c r="B175" s="33" t="s">
         <v>58</v>
       </c>
@@ -19131,7 +19105,7 @@
       </c>
     </row>
     <row r="176" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A176" s="134"/>
+      <c r="A176" s="130"/>
       <c r="B176" s="33" t="s">
         <v>59</v>
       </c>
@@ -19219,7 +19193,7 @@
       </c>
     </row>
     <row r="177" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A177" s="134" t="s">
+      <c r="A177" s="130" t="s">
         <v>36</v>
       </c>
       <c r="B177" s="33" t="s">
@@ -19312,7 +19286,7 @@
       </c>
     </row>
     <row r="178" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A178" s="134"/>
+      <c r="A178" s="130"/>
       <c r="B178" s="33" t="s">
         <v>30</v>
       </c>
@@ -19403,7 +19377,7 @@
       </c>
     </row>
     <row r="179" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A179" s="134"/>
+      <c r="A179" s="130"/>
       <c r="B179" s="33" t="s">
         <v>31</v>
       </c>
@@ -19494,7 +19468,7 @@
       </c>
     </row>
     <row r="180" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A180" s="134"/>
+      <c r="A180" s="130"/>
       <c r="B180" s="33" t="s">
         <v>49</v>
       </c>
@@ -19585,7 +19559,7 @@
       </c>
     </row>
     <row r="181" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A181" s="134"/>
+      <c r="A181" s="130"/>
       <c r="B181" s="33" t="s">
         <v>50</v>
       </c>
@@ -19676,7 +19650,7 @@
       </c>
     </row>
     <row r="182" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A182" s="134"/>
+      <c r="A182" s="130"/>
       <c r="B182" s="33" t="s">
         <v>51</v>
       </c>
@@ -19767,7 +19741,7 @@
       </c>
     </row>
     <row r="183" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A183" s="134"/>
+      <c r="A183" s="130"/>
       <c r="B183" s="33" t="s">
         <v>52</v>
       </c>
@@ -19858,7 +19832,7 @@
       </c>
     </row>
     <row r="184" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A184" s="134"/>
+      <c r="A184" s="130"/>
       <c r="B184" s="33" t="s">
         <v>53</v>
       </c>
@@ -19949,7 +19923,7 @@
       </c>
     </row>
     <row r="185" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A185" s="134"/>
+      <c r="A185" s="130"/>
       <c r="B185" s="33" t="s">
         <v>54</v>
       </c>
@@ -20040,7 +20014,7 @@
       </c>
     </row>
     <row r="186" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A186" s="134"/>
+      <c r="A186" s="130"/>
       <c r="B186" s="33" t="s">
         <v>55</v>
       </c>
@@ -20131,7 +20105,7 @@
       </c>
     </row>
     <row r="187" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A187" s="134"/>
+      <c r="A187" s="130"/>
       <c r="B187" s="33" t="s">
         <v>56</v>
       </c>
@@ -20222,7 +20196,7 @@
       </c>
     </row>
     <row r="188" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A188" s="134"/>
+      <c r="A188" s="130"/>
       <c r="B188" s="33" t="s">
         <v>57</v>
       </c>
@@ -20313,7 +20287,7 @@
       </c>
     </row>
     <row r="189" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A189" s="134"/>
+      <c r="A189" s="130"/>
       <c r="B189" s="33" t="s">
         <v>58</v>
       </c>
@@ -20404,7 +20378,7 @@
       </c>
     </row>
     <row r="190" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A190" s="134"/>
+      <c r="A190" s="130"/>
       <c r="B190" s="33" t="s">
         <v>59</v>
       </c>
@@ -20495,7 +20469,7 @@
       </c>
     </row>
     <row r="191" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A191" s="134" t="s">
+      <c r="A191" s="130" t="s">
         <v>37</v>
       </c>
       <c r="B191" s="33" t="s">
@@ -20588,7 +20562,7 @@
       </c>
     </row>
     <row r="192" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A192" s="134"/>
+      <c r="A192" s="130"/>
       <c r="B192" s="33" t="s">
         <v>30</v>
       </c>
@@ -20679,7 +20653,7 @@
       </c>
     </row>
     <row r="193" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A193" s="134"/>
+      <c r="A193" s="130"/>
       <c r="B193" s="33" t="s">
         <v>31</v>
       </c>
@@ -20770,7 +20744,7 @@
       </c>
     </row>
     <row r="194" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A194" s="134"/>
+      <c r="A194" s="130"/>
       <c r="B194" s="33" t="s">
         <v>49</v>
       </c>
@@ -20861,7 +20835,7 @@
       </c>
     </row>
     <row r="195" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A195" s="134"/>
+      <c r="A195" s="130"/>
       <c r="B195" s="33" t="s">
         <v>50</v>
       </c>
@@ -20949,7 +20923,7 @@
       </c>
     </row>
     <row r="196" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A196" s="134"/>
+      <c r="A196" s="130"/>
       <c r="B196" s="33" t="s">
         <v>51</v>
       </c>
@@ -21040,7 +21014,7 @@
       </c>
     </row>
     <row r="197" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A197" s="134"/>
+      <c r="A197" s="130"/>
       <c r="B197" s="33" t="s">
         <v>52</v>
       </c>
@@ -21131,7 +21105,7 @@
       </c>
     </row>
     <row r="198" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A198" s="134"/>
+      <c r="A198" s="130"/>
       <c r="B198" s="33" t="s">
         <v>53</v>
       </c>
@@ -21222,7 +21196,7 @@
       </c>
     </row>
     <row r="199" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A199" s="134"/>
+      <c r="A199" s="130"/>
       <c r="B199" s="33" t="s">
         <v>54</v>
       </c>
@@ -21313,7 +21287,7 @@
       </c>
     </row>
     <row r="200" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A200" s="134"/>
+      <c r="A200" s="130"/>
       <c r="B200" s="33" t="s">
         <v>55</v>
       </c>
@@ -21404,7 +21378,7 @@
       </c>
     </row>
     <row r="201" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A201" s="134"/>
+      <c r="A201" s="130"/>
       <c r="B201" s="33" t="s">
         <v>56</v>
       </c>
@@ -21495,7 +21469,7 @@
       </c>
     </row>
     <row r="202" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A202" s="134"/>
+      <c r="A202" s="130"/>
       <c r="B202" s="33" t="s">
         <v>57</v>
       </c>
@@ -21586,7 +21560,7 @@
       </c>
     </row>
     <row r="203" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A203" s="134"/>
+      <c r="A203" s="130"/>
       <c r="B203" s="33" t="s">
         <v>58</v>
       </c>
@@ -21677,7 +21651,7 @@
       </c>
     </row>
     <row r="204" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A204" s="134"/>
+      <c r="A204" s="130"/>
       <c r="B204" s="33" t="s">
         <v>59</v>
       </c>
@@ -21768,10 +21742,10 @@
       </c>
     </row>
     <row r="205" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A205" s="135" t="s">
+      <c r="A205" s="131" t="s">
         <v>38</v>
       </c>
-      <c r="B205" s="135"/>
+      <c r="B205" s="131"/>
       <c r="C205" s="44" t="s">
         <v>25</v>
       </c>
@@ -21859,10 +21833,10 @@
       </c>
     </row>
     <row r="206" spans="1:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A206" s="136" t="s">
+      <c r="A206" s="132" t="s">
         <v>39</v>
       </c>
-      <c r="B206" s="137"/>
+      <c r="B206" s="133"/>
       <c r="C206" s="47" t="s">
         <v>25</v>
       </c>
@@ -22066,36 +22040,36 @@
       </c>
     </row>
     <row r="210" spans="4:31" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="D210" s="138" t="s">
+      <c r="D210" s="129" t="s">
         <v>72</v>
       </c>
-      <c r="E210" s="138"/>
-      <c r="F210" s="138"/>
-      <c r="G210" s="138"/>
-      <c r="H210" s="138"/>
-      <c r="I210" s="138"/>
-      <c r="J210" s="138"/>
-      <c r="K210" s="138"/>
-      <c r="L210" s="138"/>
-      <c r="M210" s="138"/>
-      <c r="N210" s="138"/>
-      <c r="O210" s="138"/>
-      <c r="P210" s="138"/>
-      <c r="Q210" s="138"/>
-      <c r="R210" s="138"/>
-      <c r="S210" s="138"/>
-      <c r="T210" s="138"/>
-      <c r="U210" s="138"/>
-      <c r="V210" s="138"/>
-      <c r="W210" s="138"/>
-      <c r="X210" s="138"/>
-      <c r="Y210" s="138"/>
-      <c r="Z210" s="138"/>
-      <c r="AA210" s="138"/>
-      <c r="AB210" s="138"/>
-      <c r="AC210" s="138"/>
-      <c r="AD210" s="138"/>
-      <c r="AE210" s="138"/>
+      <c r="E210" s="129"/>
+      <c r="F210" s="129"/>
+      <c r="G210" s="129"/>
+      <c r="H210" s="129"/>
+      <c r="I210" s="129"/>
+      <c r="J210" s="129"/>
+      <c r="K210" s="129"/>
+      <c r="L210" s="129"/>
+      <c r="M210" s="129"/>
+      <c r="N210" s="129"/>
+      <c r="O210" s="129"/>
+      <c r="P210" s="129"/>
+      <c r="Q210" s="129"/>
+      <c r="R210" s="129"/>
+      <c r="S210" s="129"/>
+      <c r="T210" s="129"/>
+      <c r="U210" s="129"/>
+      <c r="V210" s="129"/>
+      <c r="W210" s="129"/>
+      <c r="X210" s="129"/>
+      <c r="Y210" s="129"/>
+      <c r="Z210" s="129"/>
+      <c r="AA210" s="129"/>
+      <c r="AB210" s="129"/>
+      <c r="AC210" s="129"/>
+      <c r="AD210" s="129"/>
+      <c r="AE210" s="129"/>
     </row>
     <row r="211" spans="4:31" ht="52.2" x14ac:dyDescent="0.3">
       <c r="D211" s="65"/>
@@ -22428,32 +22402,6 @@
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="A207:C207"/>
-    <mergeCell ref="D210:AE210"/>
-    <mergeCell ref="A163:A176"/>
-    <mergeCell ref="A177:A190"/>
-    <mergeCell ref="A191:A204"/>
-    <mergeCell ref="A205:B205"/>
-    <mergeCell ref="A206:B206"/>
-    <mergeCell ref="A116:B116"/>
-    <mergeCell ref="A117:B117"/>
-    <mergeCell ref="A118:A132"/>
-    <mergeCell ref="A133:A147"/>
-    <mergeCell ref="A148:A162"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="E11:G11"/>
-    <mergeCell ref="A114:B114"/>
-    <mergeCell ref="A115:B115"/>
-    <mergeCell ref="A110:C110"/>
-    <mergeCell ref="A21:A35"/>
-    <mergeCell ref="A36:A50"/>
-    <mergeCell ref="A51:A65"/>
-    <mergeCell ref="A66:A79"/>
-    <mergeCell ref="A80:A93"/>
-    <mergeCell ref="A94:A107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="A109:B109"/>
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A18:B18"/>
@@ -22470,6 +22418,32 @@
     <mergeCell ref="K8:L8"/>
     <mergeCell ref="K9:L9"/>
     <mergeCell ref="K10:L10"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="A114:B114"/>
+    <mergeCell ref="A115:B115"/>
+    <mergeCell ref="A110:C110"/>
+    <mergeCell ref="A21:A35"/>
+    <mergeCell ref="A36:A50"/>
+    <mergeCell ref="A51:A65"/>
+    <mergeCell ref="A66:A79"/>
+    <mergeCell ref="A80:A93"/>
+    <mergeCell ref="A94:A107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="A116:B116"/>
+    <mergeCell ref="A117:B117"/>
+    <mergeCell ref="A118:A132"/>
+    <mergeCell ref="A133:A147"/>
+    <mergeCell ref="A148:A162"/>
+    <mergeCell ref="A207:C207"/>
+    <mergeCell ref="D210:AE210"/>
+    <mergeCell ref="A163:A176"/>
+    <mergeCell ref="A177:A190"/>
+    <mergeCell ref="A191:A204"/>
+    <mergeCell ref="A205:B205"/>
+    <mergeCell ref="A206:B206"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -22493,20 +22467,20 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="108" t="s">
+      <c r="B1" s="149" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="149"/>
+      <c r="G1" s="149"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="149"/>
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="149"/>
+      <c r="M1" s="149"/>
     </row>
     <row r="2" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -22566,14 +22540,14 @@
       <c r="M4" s="4"/>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B6" s="113" t="s">
+      <c r="B6" s="150" t="s">
         <v>74</v>
       </c>
-      <c r="C6" s="114"/>
-      <c r="D6" s="114"/>
-      <c r="E6" s="114"/>
-      <c r="F6" s="114"/>
-      <c r="G6" s="112"/>
+      <c r="C6" s="151"/>
+      <c r="D6" s="151"/>
+      <c r="E6" s="151"/>
+      <c r="F6" s="151"/>
+      <c r="G6" s="137"/>
     </row>
     <row r="7" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B7" s="5" t="s">
@@ -22585,11 +22559,11 @@
       <c r="D7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="115" t="s">
+      <c r="E7" s="152" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="116"/>
-      <c r="G7" s="117"/>
+      <c r="F7" s="153"/>
+      <c r="G7" s="154"/>
     </row>
     <row r="8" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B8" s="7">
@@ -22602,17 +22576,17 @@
         <f>SUM(SUM(D114,D116,D117,D132,D147,D162,D205,D206)/5+SUM(D148,D151,D155,D177,D180,D184)/3+SUM(D153,D156,D158,D182,D185,D187,D160,D189)/2+SUM(D118,D123,D129,D133,D139,D163,D169,D191,D197,D130,D146,D204,D176))</f>
         <v>78.233333333333334</v>
       </c>
-      <c r="E8" s="118">
+      <c r="E8" s="146">
         <f>SUM(SUM(E17,E19,E20,E35,E50,E65,E108,E109)/5+SUM(E51,E54,E58,E80,E83,E87)/3+SUM(E56,E59,E61,E85,E88,E90,E63,E92)/2+SUM(E21,E26,E36,E42,E66,E72,E94,E100,E32,E107,E79,E49,E33))</f>
         <v>76</v>
       </c>
-      <c r="F8" s="119"/>
-      <c r="G8" s="120"/>
+      <c r="F8" s="147"/>
+      <c r="G8" s="148"/>
       <c r="J8" s="13"/>
-      <c r="K8" s="123" t="s">
+      <c r="K8" s="143" t="s">
         <v>16</v>
       </c>
-      <c r="L8" s="124"/>
+      <c r="L8" s="144"/>
     </row>
     <row r="9" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B9" s="10">
@@ -22625,17 +22599,17 @@
         <f>SUM(SUM(D114,D116,D117,D132,D147,D162,D205,D206)/5+SUM(D148,D152,D154,D155,D159,D177,D181,D184,D188,D183,D161,D190)/3+SUM(D125,D150,D156,D179,D185)/2+SUM(D200,D198,D193,D172,D170,D165,D142,D140,D135,D127,D120))</f>
         <v>83.4</v>
       </c>
-      <c r="E9" s="118">
+      <c r="E9" s="146">
         <f>SUM(SUM(E17,E19,E20,E35,E50,E65,E108,E109)/5+SUM(E51,E55,E57,E58,E62,E80,E84,E86,E87,E91,E64,E93)/3+SUM(E28,E53,E59,E82,E88)/2+SUM(E23,E30,E38,E43,E45,E68,E73,E75,E96,E101,E103))</f>
         <v>77.166666666666671</v>
       </c>
-      <c r="F9" s="119"/>
-      <c r="G9" s="120"/>
+      <c r="F9" s="147"/>
+      <c r="G9" s="148"/>
       <c r="J9" s="14"/>
-      <c r="K9" s="123" t="s">
+      <c r="K9" s="143" t="s">
         <v>17</v>
       </c>
-      <c r="L9" s="124"/>
+      <c r="L9" s="144"/>
     </row>
     <row r="10" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B10" s="10">
@@ -22648,17 +22622,17 @@
         <f>SUM(SUM(D114,D116,D117,D132,D147,D162,D205,D206)/5+SUM(D155,D157,D159,D184,D186,D188,D161,D190)/3+SUM(D125,D149,D150,D153,D179,D178,D182)/2+SUM(D202,D195,D192,D174,D167,D164,D144,D137,D134,D128,D119,D131))</f>
         <v>77.400000000000006</v>
       </c>
-      <c r="E10" s="118">
+      <c r="E10" s="146">
         <f>SUM(SUM(E17,E19,E20,E35,E50,E65,E108,E109)/5+SUM(E58,E60,E62,E87,E89,E91,E64,E93)/3+SUM(E28,E52,E53,E56,E81,E82,E85)/2+SUM(E22,E31,E37,E40,E47,E67,E70,E77,E95,E98,E105,E34))</f>
         <v>77.833333333333329</v>
       </c>
-      <c r="F10" s="119"/>
-      <c r="G10" s="120"/>
+      <c r="F10" s="147"/>
+      <c r="G10" s="148"/>
       <c r="J10" s="15"/>
-      <c r="K10" s="123" t="s">
+      <c r="K10" s="143" t="s">
         <v>18</v>
       </c>
-      <c r="L10" s="124"/>
+      <c r="L10" s="144"/>
     </row>
     <row r="11" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B11" s="10">
@@ -22671,17 +22645,17 @@
         <f>SUM(SUM(D114,D116,D117,D132,D147,D162,D205,D206)/5+SUM(D151,D152,D154,D157,D180,D181,D183,D186)/3+SUM(D121,D126,D149,D158,D178,D187,D160,D189)/2+SUM(D115,D122,D136,D141,D166,D171,D194,D199))</f>
         <v>69.066666666666663</v>
       </c>
-      <c r="E11" s="118">
+      <c r="E11" s="146">
         <f>SUM(SUM(E17,E19,E20,E35,E50,E65,E108,E109)/5+SUM(E54,E57,E55,E60,E83,E84,E86,E89)/3+SUM(E24,E29,E52,E61,E81,E90,E63,E92)/2+SUM(E18,E25,E39,E44,E69,E74,E97,E102))</f>
         <v>68.166666666666671</v>
       </c>
-      <c r="F11" s="119"/>
-      <c r="G11" s="120"/>
+      <c r="F11" s="147"/>
+      <c r="G11" s="148"/>
       <c r="J11" s="16"/>
-      <c r="K11" s="123" t="s">
+      <c r="K11" s="143" t="s">
         <v>19</v>
       </c>
-      <c r="L11" s="124"/>
+      <c r="L11" s="144"/>
     </row>
     <row r="12" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B12" s="10">
@@ -22694,33 +22668,33 @@
         <f>SUM(SUM(D114,D116,D117,D132,D147,D162,D205,D206)/5+SUM(D148,D151,D152,D154,D157,D159,D177,D180,D181,D183,D186,D188,D161,D190)/3+SUM(D121,D126)/2+SUM(D124,D138,D143,D168,D173,D196,D201,D175,D145,D203))</f>
         <v>61.9</v>
       </c>
-      <c r="E12" s="118">
+      <c r="E12" s="146">
         <f>SUM(SUM(E17,E19,E20,E35,E50,E65,E108,E109)/5+SUM(E51,E54,E57,E55,E60,E62,E80,E83,E84,E86,E89,E91,E64,E93)/3+SUM(E24,E29)/2+SUM(E27,E41,E46,E71,E76,E99,E104,E48,E78,E106))</f>
         <v>60.833333333333336</v>
       </c>
-      <c r="F12" s="119"/>
-      <c r="G12" s="120"/>
+      <c r="F12" s="147"/>
+      <c r="G12" s="148"/>
       <c r="J12" s="17"/>
-      <c r="K12" s="125" t="s">
+      <c r="K12" s="145" t="s">
         <v>20</v>
       </c>
-      <c r="L12" s="125"/>
+      <c r="L12" s="145"/>
     </row>
     <row r="13" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B13" s="121" t="s">
+      <c r="B13" s="155" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="122"/>
+      <c r="C13" s="156"/>
       <c r="D13" s="12">
         <f>SUM(D8:D12)</f>
         <v>370</v>
       </c>
-      <c r="E13" s="121">
+      <c r="E13" s="155">
         <f>SUM(E8:G12)</f>
         <v>360</v>
       </c>
-      <c r="F13" s="122"/>
-      <c r="G13" s="122"/>
+      <c r="F13" s="156"/>
+      <c r="G13" s="156"/>
     </row>
     <row r="16" spans="1:32" ht="52.2" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
@@ -22847,10 +22821,10 @@
       </c>
     </row>
     <row r="17" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="109" t="s">
+      <c r="A17" s="134" t="s">
         <v>75</v>
       </c>
-      <c r="B17" s="110"/>
+      <c r="B17" s="135"/>
       <c r="C17" s="22" t="s">
         <v>25</v>
       </c>
@@ -22941,10 +22915,10 @@
       </c>
     </row>
     <row r="18" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="109" t="s">
+      <c r="A18" s="134" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="110"/>
+      <c r="B18" s="135"/>
       <c r="C18" s="27" t="s">
         <v>40</v>
       </c>
@@ -23035,10 +23009,10 @@
       </c>
     </row>
     <row r="19" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="109" t="s">
+      <c r="A19" s="134" t="s">
         <v>76</v>
       </c>
-      <c r="B19" s="110"/>
+      <c r="B19" s="135"/>
       <c r="C19" s="22" t="s">
         <v>25</v>
       </c>
@@ -23129,10 +23103,10 @@
       </c>
     </row>
     <row r="20" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="111" t="s">
+      <c r="A20" s="136" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="139"/>
+      <c r="B20" s="157"/>
       <c r="C20" s="27" t="s">
         <v>25</v>
       </c>
@@ -23223,7 +23197,7 @@
       </c>
     </row>
     <row r="21" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="140" t="s">
+      <c r="A21" s="158" t="s">
         <v>29</v>
       </c>
       <c r="B21" s="73" t="s">
@@ -23319,7 +23293,7 @@
       </c>
     </row>
     <row r="22" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="141"/>
+      <c r="A22" s="159"/>
       <c r="B22" s="73" t="s">
         <v>78</v>
       </c>
@@ -23413,7 +23387,7 @@
       </c>
     </row>
     <row r="23" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="141"/>
+      <c r="A23" s="159"/>
       <c r="B23" s="74" t="s">
         <v>79</v>
       </c>
@@ -23507,7 +23481,7 @@
       </c>
     </row>
     <row r="24" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="141"/>
+      <c r="A24" s="159"/>
       <c r="B24" s="75" t="s">
         <v>80</v>
       </c>
@@ -23598,7 +23572,7 @@
       </c>
     </row>
     <row r="25" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="141"/>
+      <c r="A25" s="159"/>
       <c r="B25" s="74" t="s">
         <v>81</v>
       </c>
@@ -23692,7 +23666,7 @@
       </c>
     </row>
     <row r="26" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="141"/>
+      <c r="A26" s="159"/>
       <c r="B26" s="74" t="s">
         <v>82</v>
       </c>
@@ -23786,7 +23760,7 @@
       </c>
     </row>
     <row r="27" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="141"/>
+      <c r="A27" s="159"/>
       <c r="B27" s="76" t="s">
         <v>83</v>
       </c>
@@ -23880,7 +23854,7 @@
       </c>
     </row>
     <row r="28" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="141"/>
+      <c r="A28" s="159"/>
       <c r="B28" s="76" t="s">
         <v>84</v>
       </c>
@@ -23974,7 +23948,7 @@
       </c>
     </row>
     <row r="29" spans="1:32" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="141"/>
+      <c r="A29" s="159"/>
       <c r="B29" s="76" t="s">
         <v>85</v>
       </c>
@@ -24068,7 +24042,7 @@
       </c>
     </row>
     <row r="30" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="141"/>
+      <c r="A30" s="159"/>
       <c r="B30" s="76" t="s">
         <v>86</v>
       </c>
@@ -24162,7 +24136,7 @@
       </c>
     </row>
     <row r="31" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="141"/>
+      <c r="A31" s="159"/>
       <c r="B31" s="76" t="s">
         <v>87</v>
       </c>
@@ -24256,8 +24230,8 @@
       </c>
     </row>
     <row r="32" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="141"/>
-      <c r="B32" s="143" t="s">
+      <c r="A32" s="159"/>
+      <c r="B32" s="104" t="s">
         <v>88</v>
       </c>
       <c r="C32" s="77" t="s">
@@ -24279,19 +24253,19 @@
       <c r="I32" s="77">
         <v>1</v>
       </c>
-      <c r="J32" s="144">
+      <c r="J32" s="105">
         <v>0</v>
       </c>
       <c r="K32" s="57">
         <v>0</v>
       </c>
-      <c r="L32" s="145">
-        <v>0</v>
-      </c>
-      <c r="M32" s="145">
-        <v>0</v>
-      </c>
-      <c r="N32" s="146">
+      <c r="L32" s="106">
+        <v>0</v>
+      </c>
+      <c r="M32" s="106">
+        <v>0</v>
+      </c>
+      <c r="N32" s="107">
         <v>0</v>
       </c>
       <c r="O32" s="38">
@@ -24349,15 +24323,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:40" s="154" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="141"/>
+    <row r="33" spans="1:40" s="114" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="159"/>
       <c r="B33" s="76" t="s">
         <v>107</v>
       </c>
       <c r="C33" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="D33" s="157"/>
+      <c r="D33" s="116"/>
       <c r="E33" s="24">
         <v>2</v>
       </c>
@@ -24373,19 +24347,19 @@
       <c r="I33" s="24">
         <v>2</v>
       </c>
-      <c r="J33" s="144">
+      <c r="J33" s="105">
         <v>0</v>
       </c>
       <c r="K33" s="57">
         <v>0</v>
       </c>
-      <c r="L33" s="145">
-        <v>0</v>
-      </c>
-      <c r="M33" s="145">
-        <v>0</v>
-      </c>
-      <c r="N33" s="146">
+      <c r="L33" s="106">
+        <v>0</v>
+      </c>
+      <c r="M33" s="106">
+        <v>0</v>
+      </c>
+      <c r="N33" s="107">
         <v>0</v>
       </c>
       <c r="O33" s="38">
@@ -24442,24 +24416,24 @@
       <c r="AF33" s="38">
         <v>0</v>
       </c>
-      <c r="AG33" s="156"/>
-      <c r="AH33" s="156"/>
-      <c r="AI33" s="156"/>
-      <c r="AJ33" s="156"/>
-      <c r="AK33" s="156"/>
-      <c r="AL33" s="156"/>
-      <c r="AM33" s="156"/>
-      <c r="AN33" s="155"/>
-    </row>
-    <row r="34" spans="1:40" s="154" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="141"/>
+      <c r="AG33"/>
+      <c r="AH33"/>
+      <c r="AI33"/>
+      <c r="AJ33"/>
+      <c r="AK33"/>
+      <c r="AL33"/>
+      <c r="AM33"/>
+      <c r="AN33" s="115"/>
+    </row>
+    <row r="34" spans="1:40" s="114" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="159"/>
       <c r="B34" s="76" t="s">
         <v>108</v>
       </c>
       <c r="C34" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="D34" s="157"/>
+      <c r="D34" s="116"/>
       <c r="E34" s="24">
         <v>2</v>
       </c>
@@ -24475,19 +24449,19 @@
       <c r="I34" s="24">
         <v>2</v>
       </c>
-      <c r="J34" s="144">
+      <c r="J34" s="105">
         <v>0</v>
       </c>
       <c r="K34" s="57">
         <v>0</v>
       </c>
-      <c r="L34" s="145">
-        <v>0</v>
-      </c>
-      <c r="M34" s="145">
-        <v>0</v>
-      </c>
-      <c r="N34" s="146">
+      <c r="L34" s="106">
+        <v>0</v>
+      </c>
+      <c r="M34" s="106">
+        <v>0</v>
+      </c>
+      <c r="N34" s="107">
         <v>0</v>
       </c>
       <c r="O34" s="38">
@@ -24544,24 +24518,24 @@
       <c r="AF34" s="38">
         <v>0</v>
       </c>
-      <c r="AG34" s="156"/>
-      <c r="AH34" s="156"/>
-      <c r="AI34" s="156"/>
-      <c r="AJ34" s="156"/>
-      <c r="AK34" s="156"/>
-      <c r="AL34" s="156"/>
-      <c r="AM34" s="156"/>
-      <c r="AN34" s="155"/>
+      <c r="AG34"/>
+      <c r="AH34"/>
+      <c r="AI34"/>
+      <c r="AJ34"/>
+      <c r="AK34"/>
+      <c r="AL34"/>
+      <c r="AM34"/>
+      <c r="AN34" s="115"/>
     </row>
     <row r="35" spans="1:40" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="142"/>
-      <c r="B35" s="147" t="s">
+      <c r="A35" s="160"/>
+      <c r="B35" s="108" t="s">
         <v>32</v>
       </c>
       <c r="C35" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="D35" s="148"/>
+      <c r="D35" s="89"/>
       <c r="E35" s="78">
         <v>10</v>
       </c>
@@ -24580,75 +24554,75 @@
       <c r="J35" s="58">
         <v>10</v>
       </c>
-      <c r="K35" s="149">
+      <c r="K35" s="109">
         <v>0</v>
       </c>
       <c r="L35" s="58">
         <v>0</v>
       </c>
-      <c r="M35" s="150">
-        <v>0</v>
-      </c>
-      <c r="N35" s="150">
-        <v>0</v>
-      </c>
-      <c r="O35" s="151">
-        <v>0</v>
-      </c>
-      <c r="P35" s="152">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="152">
-        <v>0</v>
-      </c>
-      <c r="R35" s="152">
-        <v>0</v>
-      </c>
-      <c r="S35" s="152">
-        <v>0</v>
-      </c>
-      <c r="T35" s="152">
-        <v>0</v>
-      </c>
-      <c r="U35" s="152">
-        <v>0</v>
-      </c>
-      <c r="V35" s="152">
-        <v>0</v>
-      </c>
-      <c r="W35" s="152">
-        <v>0</v>
-      </c>
-      <c r="X35" s="152">
-        <v>0</v>
-      </c>
-      <c r="Y35" s="152">
-        <v>0</v>
-      </c>
-      <c r="Z35" s="152">
-        <v>0</v>
-      </c>
-      <c r="AA35" s="152">
-        <v>0</v>
-      </c>
-      <c r="AB35" s="152">
-        <v>0</v>
-      </c>
-      <c r="AC35" s="152">
-        <v>0</v>
-      </c>
-      <c r="AD35" s="152">
-        <v>0</v>
-      </c>
-      <c r="AE35" s="152">
-        <v>0</v>
-      </c>
-      <c r="AF35" s="152">
+      <c r="M35" s="110">
+        <v>0</v>
+      </c>
+      <c r="N35" s="110">
+        <v>0</v>
+      </c>
+      <c r="O35" s="111">
+        <v>0</v>
+      </c>
+      <c r="P35" s="112">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="112">
+        <v>0</v>
+      </c>
+      <c r="R35" s="112">
+        <v>0</v>
+      </c>
+      <c r="S35" s="112">
+        <v>0</v>
+      </c>
+      <c r="T35" s="112">
+        <v>0</v>
+      </c>
+      <c r="U35" s="112">
+        <v>0</v>
+      </c>
+      <c r="V35" s="112">
+        <v>0</v>
+      </c>
+      <c r="W35" s="112">
+        <v>0</v>
+      </c>
+      <c r="X35" s="112">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="112">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="112">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="112">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="112">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="112">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="112">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="112">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="112">
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:40" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="132" t="s">
+      <c r="A36" s="141" t="s">
         <v>33</v>
       </c>
       <c r="B36" s="73" t="s">
@@ -24744,7 +24718,7 @@
       </c>
     </row>
     <row r="37" spans="1:40" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="133"/>
+      <c r="A37" s="142"/>
       <c r="B37" s="73" t="s">
         <v>78</v>
       </c>
@@ -24838,7 +24812,7 @@
       </c>
     </row>
     <row r="38" spans="1:40" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A38" s="133"/>
+      <c r="A38" s="142"/>
       <c r="B38" s="74" t="s">
         <v>79</v>
       </c>
@@ -24932,7 +24906,7 @@
       </c>
     </row>
     <row r="39" spans="1:40" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A39" s="133"/>
+      <c r="A39" s="142"/>
       <c r="B39" s="75" t="s">
         <v>80</v>
       </c>
@@ -25026,7 +25000,7 @@
       </c>
     </row>
     <row r="40" spans="1:40" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A40" s="133"/>
+      <c r="A40" s="142"/>
       <c r="B40" s="74" t="s">
         <v>81</v>
       </c>
@@ -25120,7 +25094,7 @@
       </c>
     </row>
     <row r="41" spans="1:40" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A41" s="133"/>
+      <c r="A41" s="142"/>
       <c r="B41" s="74" t="s">
         <v>82</v>
       </c>
@@ -25214,7 +25188,7 @@
       </c>
     </row>
     <row r="42" spans="1:40" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A42" s="133"/>
+      <c r="A42" s="142"/>
       <c r="B42" s="76" t="s">
         <v>83</v>
       </c>
@@ -25308,7 +25282,7 @@
       </c>
     </row>
     <row r="43" spans="1:40" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A43" s="133"/>
+      <c r="A43" s="142"/>
       <c r="B43" s="76" t="s">
         <v>84</v>
       </c>
@@ -25402,7 +25376,7 @@
       </c>
     </row>
     <row r="44" spans="1:40" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="133"/>
+      <c r="A44" s="142"/>
       <c r="B44" s="76" t="s">
         <v>85</v>
       </c>
@@ -25496,7 +25470,7 @@
       </c>
     </row>
     <row r="45" spans="1:40" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A45" s="133"/>
+      <c r="A45" s="142"/>
       <c r="B45" s="76" t="s">
         <v>86</v>
       </c>
@@ -25590,7 +25564,7 @@
       </c>
     </row>
     <row r="46" spans="1:40" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A46" s="133"/>
+      <c r="A46" s="142"/>
       <c r="B46" s="76" t="s">
         <v>87</v>
       </c>
@@ -25684,7 +25658,7 @@
       </c>
     </row>
     <row r="47" spans="1:40" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A47" s="133"/>
+      <c r="A47" s="142"/>
       <c r="B47" s="76" t="s">
         <v>88</v>
       </c>
@@ -25778,7 +25752,7 @@
       </c>
     </row>
     <row r="48" spans="1:40" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A48" s="133"/>
+      <c r="A48" s="142"/>
       <c r="B48" s="76" t="s">
         <v>107</v>
       </c>
@@ -25872,7 +25846,7 @@
       </c>
     </row>
     <row r="49" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A49" s="133"/>
+      <c r="A49" s="142"/>
       <c r="B49" s="76" t="s">
         <v>108</v>
       </c>
@@ -25966,11 +25940,11 @@
       </c>
     </row>
     <row r="50" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="133"/>
+      <c r="A50" s="142"/>
       <c r="B50" s="73" t="s">
         <v>32</v>
       </c>
-      <c r="C50" s="152" t="s">
+      <c r="C50" s="112" t="s">
         <v>25</v>
       </c>
       <c r="D50" s="36"/>
@@ -26060,7 +26034,7 @@
       </c>
     </row>
     <row r="51" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A51" s="134" t="s">
+      <c r="A51" s="130" t="s">
         <v>34</v>
       </c>
       <c r="B51" s="73" t="s">
@@ -26156,7 +26130,7 @@
       </c>
     </row>
     <row r="52" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A52" s="134"/>
+      <c r="A52" s="130"/>
       <c r="B52" s="73" t="s">
         <v>78</v>
       </c>
@@ -26250,7 +26224,7 @@
       </c>
     </row>
     <row r="53" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A53" s="134"/>
+      <c r="A53" s="130"/>
       <c r="B53" s="74" t="s">
         <v>79</v>
       </c>
@@ -26344,7 +26318,7 @@
       </c>
     </row>
     <row r="54" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A54" s="134"/>
+      <c r="A54" s="130"/>
       <c r="B54" s="75" t="s">
         <v>80</v>
       </c>
@@ -26438,7 +26412,7 @@
       </c>
     </row>
     <row r="55" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A55" s="134"/>
+      <c r="A55" s="130"/>
       <c r="B55" s="74" t="s">
         <v>81</v>
       </c>
@@ -26532,7 +26506,7 @@
       </c>
     </row>
     <row r="56" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="134"/>
+      <c r="A56" s="130"/>
       <c r="B56" s="74" t="s">
         <v>82</v>
       </c>
@@ -26626,7 +26600,7 @@
       </c>
     </row>
     <row r="57" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A57" s="134"/>
+      <c r="A57" s="130"/>
       <c r="B57" s="76" t="s">
         <v>83</v>
       </c>
@@ -26720,7 +26694,7 @@
       </c>
     </row>
     <row r="58" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A58" s="134"/>
+      <c r="A58" s="130"/>
       <c r="B58" s="76" t="s">
         <v>84</v>
       </c>
@@ -26814,7 +26788,7 @@
       </c>
     </row>
     <row r="59" spans="1:32" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A59" s="134"/>
+      <c r="A59" s="130"/>
       <c r="B59" s="76" t="s">
         <v>85</v>
       </c>
@@ -26908,7 +26882,7 @@
       </c>
     </row>
     <row r="60" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A60" s="134"/>
+      <c r="A60" s="130"/>
       <c r="B60" s="76" t="s">
         <v>86</v>
       </c>
@@ -27002,7 +26976,7 @@
       </c>
     </row>
     <row r="61" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A61" s="134"/>
+      <c r="A61" s="130"/>
       <c r="B61" s="76" t="s">
         <v>87</v>
       </c>
@@ -27096,7 +27070,7 @@
       </c>
     </row>
     <row r="62" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A62" s="134"/>
+      <c r="A62" s="130"/>
       <c r="B62" s="76" t="s">
         <v>88</v>
       </c>
@@ -27190,7 +27164,7 @@
       </c>
     </row>
     <row r="63" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A63" s="134"/>
+      <c r="A63" s="130"/>
       <c r="B63" s="76" t="s">
         <v>107</v>
       </c>
@@ -27284,7 +27258,7 @@
       </c>
     </row>
     <row r="64" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A64" s="134"/>
+      <c r="A64" s="130"/>
       <c r="B64" s="76" t="s">
         <v>108</v>
       </c>
@@ -27378,11 +27352,11 @@
       </c>
     </row>
     <row r="65" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A65" s="134"/>
+      <c r="A65" s="130"/>
       <c r="B65" s="73" t="s">
         <v>91</v>
       </c>
-      <c r="C65" s="152" t="s">
+      <c r="C65" s="112" t="s">
         <v>25</v>
       </c>
       <c r="D65" s="43"/>
@@ -27472,7 +27446,7 @@
       </c>
     </row>
     <row r="66" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A66" s="134" t="s">
+      <c r="A66" s="130" t="s">
         <v>35</v>
       </c>
       <c r="B66" s="73" t="s">
@@ -27568,7 +27542,7 @@
       </c>
     </row>
     <row r="67" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A67" s="134"/>
+      <c r="A67" s="130"/>
       <c r="B67" s="73" t="s">
         <v>78</v>
       </c>
@@ -27662,7 +27636,7 @@
       </c>
     </row>
     <row r="68" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A68" s="134"/>
+      <c r="A68" s="130"/>
       <c r="B68" s="74" t="s">
         <v>79</v>
       </c>
@@ -27756,7 +27730,7 @@
       </c>
     </row>
     <row r="69" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A69" s="134"/>
+      <c r="A69" s="130"/>
       <c r="B69" s="75" t="s">
         <v>80</v>
       </c>
@@ -27850,7 +27824,7 @@
       </c>
     </row>
     <row r="70" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A70" s="134"/>
+      <c r="A70" s="130"/>
       <c r="B70" s="74" t="s">
         <v>81</v>
       </c>
@@ -27944,7 +27918,7 @@
       </c>
     </row>
     <row r="71" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A71" s="134"/>
+      <c r="A71" s="130"/>
       <c r="B71" s="74" t="s">
         <v>82</v>
       </c>
@@ -28038,7 +28012,7 @@
       </c>
     </row>
     <row r="72" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A72" s="134"/>
+      <c r="A72" s="130"/>
       <c r="B72" s="76" t="s">
         <v>83</v>
       </c>
@@ -28132,7 +28106,7 @@
       </c>
     </row>
     <row r="73" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A73" s="134"/>
+      <c r="A73" s="130"/>
       <c r="B73" s="76" t="s">
         <v>84</v>
       </c>
@@ -28226,7 +28200,7 @@
       </c>
     </row>
     <row r="74" spans="1:32" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="134"/>
+      <c r="A74" s="130"/>
       <c r="B74" s="76" t="s">
         <v>85</v>
       </c>
@@ -28320,7 +28294,7 @@
       </c>
     </row>
     <row r="75" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A75" s="134"/>
+      <c r="A75" s="130"/>
       <c r="B75" s="76" t="s">
         <v>86</v>
       </c>
@@ -28414,7 +28388,7 @@
       </c>
     </row>
     <row r="76" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A76" s="134"/>
+      <c r="A76" s="130"/>
       <c r="B76" s="76" t="s">
         <v>87</v>
       </c>
@@ -28508,7 +28482,7 @@
       </c>
     </row>
     <row r="77" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A77" s="134"/>
+      <c r="A77" s="130"/>
       <c r="B77" s="76" t="s">
         <v>88</v>
       </c>
@@ -28602,7 +28576,7 @@
       </c>
     </row>
     <row r="78" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A78" s="134"/>
+      <c r="A78" s="130"/>
       <c r="B78" s="76" t="s">
         <v>107</v>
       </c>
@@ -28696,7 +28670,7 @@
       </c>
     </row>
     <row r="79" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A79" s="134"/>
+      <c r="A79" s="130"/>
       <c r="B79" s="76" t="s">
         <v>108</v>
       </c>
@@ -28790,7 +28764,7 @@
       </c>
     </row>
     <row r="80" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A80" s="134" t="s">
+      <c r="A80" s="130" t="s">
         <v>36</v>
       </c>
       <c r="B80" s="73" t="s">
@@ -28886,7 +28860,7 @@
       </c>
     </row>
     <row r="81" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A81" s="134"/>
+      <c r="A81" s="130"/>
       <c r="B81" s="73" t="s">
         <v>78</v>
       </c>
@@ -28980,7 +28954,7 @@
       </c>
     </row>
     <row r="82" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A82" s="134"/>
+      <c r="A82" s="130"/>
       <c r="B82" s="74" t="s">
         <v>79</v>
       </c>
@@ -29074,7 +29048,7 @@
       </c>
     </row>
     <row r="83" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A83" s="134"/>
+      <c r="A83" s="130"/>
       <c r="B83" s="75" t="s">
         <v>80</v>
       </c>
@@ -29168,7 +29142,7 @@
       </c>
     </row>
     <row r="84" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A84" s="134"/>
+      <c r="A84" s="130"/>
       <c r="B84" s="74" t="s">
         <v>81</v>
       </c>
@@ -29262,7 +29236,7 @@
       </c>
     </row>
     <row r="85" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A85" s="134"/>
+      <c r="A85" s="130"/>
       <c r="B85" s="74" t="s">
         <v>82</v>
       </c>
@@ -29356,7 +29330,7 @@
       </c>
     </row>
     <row r="86" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A86" s="134"/>
+      <c r="A86" s="130"/>
       <c r="B86" s="76" t="s">
         <v>83</v>
       </c>
@@ -29450,7 +29424,7 @@
       </c>
     </row>
     <row r="87" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A87" s="134"/>
+      <c r="A87" s="130"/>
       <c r="B87" s="76" t="s">
         <v>84</v>
       </c>
@@ -29544,7 +29518,7 @@
       </c>
     </row>
     <row r="88" spans="1:32" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A88" s="134"/>
+      <c r="A88" s="130"/>
       <c r="B88" s="76" t="s">
         <v>85</v>
       </c>
@@ -29638,7 +29612,7 @@
       </c>
     </row>
     <row r="89" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A89" s="134"/>
+      <c r="A89" s="130"/>
       <c r="B89" s="76" t="s">
         <v>86</v>
       </c>
@@ -29732,7 +29706,7 @@
       </c>
     </row>
     <row r="90" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A90" s="134"/>
+      <c r="A90" s="130"/>
       <c r="B90" s="76" t="s">
         <v>87</v>
       </c>
@@ -29826,7 +29800,7 @@
       </c>
     </row>
     <row r="91" spans="1:32" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="134"/>
+      <c r="A91" s="130"/>
       <c r="B91" s="76" t="s">
         <v>88</v>
       </c>
@@ -29920,14 +29894,14 @@
       </c>
     </row>
     <row r="92" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A92" s="134"/>
+      <c r="A92" s="130"/>
       <c r="B92" s="76" t="s">
         <v>107</v>
       </c>
       <c r="C92" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="D92" s="161"/>
+      <c r="D92" s="117"/>
       <c r="E92" s="24">
         <v>2</v>
       </c>
@@ -30014,84 +29988,84 @@
       </c>
     </row>
     <row r="93" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A93" s="134"/>
+      <c r="A93" s="130"/>
       <c r="B93" s="76" t="s">
         <v>108</v>
       </c>
       <c r="C93" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="D93" s="155"/>
-      <c r="E93" s="159">
-        <v>2</v>
-      </c>
-      <c r="F93" s="159">
-        <v>2</v>
-      </c>
-      <c r="G93" s="159">
-        <v>2</v>
-      </c>
-      <c r="H93" s="159">
-        <v>2</v>
-      </c>
-      <c r="I93" s="159">
-        <v>2</v>
-      </c>
-      <c r="J93" s="159">
-        <v>2</v>
-      </c>
-      <c r="K93" s="159">
-        <v>2</v>
-      </c>
-      <c r="L93" s="159">
-        <v>2</v>
-      </c>
-      <c r="M93" s="159">
-        <v>2</v>
-      </c>
-      <c r="N93" s="159">
-        <v>2</v>
-      </c>
-      <c r="O93" s="159">
-        <v>2</v>
-      </c>
-      <c r="P93" s="159">
-        <v>2</v>
-      </c>
-      <c r="Q93" s="159">
-        <v>2</v>
-      </c>
-      <c r="R93" s="159">
-        <v>2</v>
-      </c>
-      <c r="S93" s="159">
-        <v>2</v>
-      </c>
-      <c r="T93" s="159">
-        <v>2</v>
-      </c>
-      <c r="U93" s="159">
-        <v>2</v>
-      </c>
-      <c r="V93" s="159">
-        <v>2</v>
-      </c>
-      <c r="W93" s="159">
-        <v>2</v>
-      </c>
-      <c r="X93" s="159">
-        <v>2</v>
-      </c>
-      <c r="Y93" s="159">
-        <v>2</v>
-      </c>
-      <c r="Z93" s="159">
-        <v>2</v>
-      </c>
-      <c r="AA93" s="159">
-        <v>2</v>
-      </c>
-      <c r="AB93" s="159">
+      <c r="D93" s="115"/>
+      <c r="E93" s="24">
+        <v>2</v>
+      </c>
+      <c r="F93" s="24">
+        <v>2</v>
+      </c>
+      <c r="G93" s="24">
+        <v>2</v>
+      </c>
+      <c r="H93" s="24">
+        <v>2</v>
+      </c>
+      <c r="I93" s="24">
+        <v>2</v>
+      </c>
+      <c r="J93" s="24">
+        <v>2</v>
+      </c>
+      <c r="K93" s="24">
+        <v>2</v>
+      </c>
+      <c r="L93" s="24">
+        <v>2</v>
+      </c>
+      <c r="M93" s="24">
+        <v>2</v>
+      </c>
+      <c r="N93" s="24">
+        <v>2</v>
+      </c>
+      <c r="O93" s="24">
+        <v>2</v>
+      </c>
+      <c r="P93" s="24">
+        <v>2</v>
+      </c>
+      <c r="Q93" s="24">
+        <v>2</v>
+      </c>
+      <c r="R93" s="24">
+        <v>2</v>
+      </c>
+      <c r="S93" s="24">
+        <v>2</v>
+      </c>
+      <c r="T93" s="24">
+        <v>2</v>
+      </c>
+      <c r="U93" s="24">
+        <v>2</v>
+      </c>
+      <c r="V93" s="24">
+        <v>2</v>
+      </c>
+      <c r="W93" s="24">
+        <v>2</v>
+      </c>
+      <c r="X93" s="24">
+        <v>2</v>
+      </c>
+      <c r="Y93" s="24">
+        <v>2</v>
+      </c>
+      <c r="Z93" s="24">
+        <v>2</v>
+      </c>
+      <c r="AA93" s="24">
+        <v>2</v>
+      </c>
+      <c r="AB93" s="24">
         <v>2</v>
       </c>
       <c r="AC93" s="25">
@@ -30108,7 +30082,7 @@
       </c>
     </row>
     <row r="94" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A94" s="134" t="s">
+      <c r="A94" s="130" t="s">
         <v>37</v>
       </c>
       <c r="B94" s="73" t="s">
@@ -30204,7 +30178,7 @@
       </c>
     </row>
     <row r="95" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A95" s="134"/>
+      <c r="A95" s="130"/>
       <c r="B95" s="73" t="s">
         <v>78</v>
       </c>
@@ -30298,7 +30272,7 @@
       </c>
     </row>
     <row r="96" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A96" s="134"/>
+      <c r="A96" s="130"/>
       <c r="B96" s="74" t="s">
         <v>79</v>
       </c>
@@ -30392,7 +30366,7 @@
       </c>
     </row>
     <row r="97" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A97" s="134"/>
+      <c r="A97" s="130"/>
       <c r="B97" s="75" t="s">
         <v>80</v>
       </c>
@@ -30486,7 +30460,7 @@
       </c>
     </row>
     <row r="98" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A98" s="134"/>
+      <c r="A98" s="130"/>
       <c r="B98" s="74" t="s">
         <v>81</v>
       </c>
@@ -30580,7 +30554,7 @@
       </c>
     </row>
     <row r="99" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A99" s="134"/>
+      <c r="A99" s="130"/>
       <c r="B99" s="74" t="s">
         <v>82</v>
       </c>
@@ -30674,7 +30648,7 @@
       </c>
     </row>
     <row r="100" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A100" s="134"/>
+      <c r="A100" s="130"/>
       <c r="B100" s="76" t="s">
         <v>83</v>
       </c>
@@ -30768,7 +30742,7 @@
       </c>
     </row>
     <row r="101" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A101" s="134"/>
+      <c r="A101" s="130"/>
       <c r="B101" s="76" t="s">
         <v>84</v>
       </c>
@@ -30862,7 +30836,7 @@
       </c>
     </row>
     <row r="102" spans="1:32" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A102" s="134"/>
+      <c r="A102" s="130"/>
       <c r="B102" s="76" t="s">
         <v>85</v>
       </c>
@@ -30956,7 +30930,7 @@
       </c>
     </row>
     <row r="103" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A103" s="134"/>
+      <c r="A103" s="130"/>
       <c r="B103" s="76" t="s">
         <v>86</v>
       </c>
@@ -31050,7 +31024,7 @@
       </c>
     </row>
     <row r="104" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A104" s="134"/>
+      <c r="A104" s="130"/>
       <c r="B104" s="76" t="s">
         <v>87</v>
       </c>
@@ -31144,11 +31118,11 @@
       </c>
     </row>
     <row r="105" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A105" s="134"/>
+      <c r="A105" s="130"/>
       <c r="B105" s="76" t="s">
         <v>88</v>
       </c>
-      <c r="C105" s="162" t="s">
+      <c r="C105" s="118" t="s">
         <v>46</v>
       </c>
       <c r="D105" s="42"/>
@@ -31238,7 +31212,7 @@
       </c>
     </row>
     <row r="106" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A106" s="134"/>
+      <c r="A106" s="130"/>
       <c r="B106" s="76" t="s">
         <v>107</v>
       </c>
@@ -31332,89 +31306,89 @@
       </c>
     </row>
     <row r="107" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A107" s="134"/>
+      <c r="A107" s="130"/>
       <c r="B107" s="76" t="s">
         <v>108</v>
       </c>
       <c r="C107" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="E107" s="160">
-        <v>1</v>
-      </c>
-      <c r="F107" s="160">
-        <v>1</v>
-      </c>
-      <c r="G107" s="160">
-        <v>1</v>
-      </c>
-      <c r="H107" s="160">
-        <v>1</v>
-      </c>
-      <c r="I107" s="160">
-        <v>1</v>
-      </c>
-      <c r="J107" s="160">
-        <v>1</v>
-      </c>
-      <c r="K107" s="160">
-        <v>1</v>
-      </c>
-      <c r="L107" s="160">
-        <v>1</v>
-      </c>
-      <c r="M107" s="160">
-        <v>1</v>
-      </c>
-      <c r="N107" s="160">
-        <v>1</v>
-      </c>
-      <c r="O107" s="160">
-        <v>1</v>
-      </c>
-      <c r="P107" s="160">
-        <v>1</v>
-      </c>
-      <c r="Q107" s="160">
-        <v>1</v>
-      </c>
-      <c r="R107" s="160">
-        <v>1</v>
-      </c>
-      <c r="S107" s="160">
-        <v>1</v>
-      </c>
-      <c r="T107" s="160">
-        <v>1</v>
-      </c>
-      <c r="U107" s="160">
-        <v>1</v>
-      </c>
-      <c r="V107" s="160">
-        <v>1</v>
-      </c>
-      <c r="W107" s="160">
-        <v>1</v>
-      </c>
-      <c r="X107" s="160">
-        <v>1</v>
-      </c>
-      <c r="Y107" s="160">
-        <v>1</v>
-      </c>
-      <c r="Z107" s="160">
-        <v>1</v>
-      </c>
-      <c r="AA107" s="160">
-        <v>1</v>
-      </c>
-      <c r="AB107" s="160">
-        <v>1</v>
-      </c>
-      <c r="AC107" s="160">
-        <v>1</v>
-      </c>
-      <c r="AD107" s="160">
+      <c r="E107" s="103">
+        <v>1</v>
+      </c>
+      <c r="F107" s="103">
+        <v>1</v>
+      </c>
+      <c r="G107" s="103">
+        <v>1</v>
+      </c>
+      <c r="H107" s="103">
+        <v>1</v>
+      </c>
+      <c r="I107" s="103">
+        <v>1</v>
+      </c>
+      <c r="J107" s="103">
+        <v>1</v>
+      </c>
+      <c r="K107" s="103">
+        <v>1</v>
+      </c>
+      <c r="L107" s="103">
+        <v>1</v>
+      </c>
+      <c r="M107" s="103">
+        <v>1</v>
+      </c>
+      <c r="N107" s="103">
+        <v>1</v>
+      </c>
+      <c r="O107" s="103">
+        <v>1</v>
+      </c>
+      <c r="P107" s="103">
+        <v>1</v>
+      </c>
+      <c r="Q107" s="103">
+        <v>1</v>
+      </c>
+      <c r="R107" s="103">
+        <v>1</v>
+      </c>
+      <c r="S107" s="103">
+        <v>1</v>
+      </c>
+      <c r="T107" s="103">
+        <v>1</v>
+      </c>
+      <c r="U107" s="103">
+        <v>1</v>
+      </c>
+      <c r="V107" s="103">
+        <v>1</v>
+      </c>
+      <c r="W107" s="103">
+        <v>1</v>
+      </c>
+      <c r="X107" s="103">
+        <v>1</v>
+      </c>
+      <c r="Y107" s="103">
+        <v>1</v>
+      </c>
+      <c r="Z107" s="103">
+        <v>1</v>
+      </c>
+      <c r="AA107" s="103">
+        <v>1</v>
+      </c>
+      <c r="AB107" s="103">
+        <v>1</v>
+      </c>
+      <c r="AC107" s="103">
+        <v>1</v>
+      </c>
+      <c r="AD107" s="103">
         <v>1</v>
       </c>
       <c r="AE107" s="25">
@@ -31425,10 +31399,10 @@
       </c>
     </row>
     <row r="108" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A108" s="135" t="s">
+      <c r="A108" s="131" t="s">
         <v>89</v>
       </c>
-      <c r="B108" s="135"/>
+      <c r="B108" s="131"/>
       <c r="C108" s="44" t="s">
         <v>25</v>
       </c>
@@ -31519,10 +31493,10 @@
       </c>
     </row>
     <row r="109" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A109" s="136" t="s">
+      <c r="A109" s="132" t="s">
         <v>90</v>
       </c>
-      <c r="B109" s="137"/>
+      <c r="B109" s="133"/>
       <c r="C109" s="47" t="s">
         <v>25</v>
       </c>
@@ -31620,111 +31594,111 @@
       <c r="C110" s="128"/>
       <c r="D110" s="49"/>
       <c r="E110" s="46">
-        <f>SUM(E17:E109)</f>
+        <f t="shared" ref="E110:AE110" si="2">SUM(E17:E109)</f>
         <v>360</v>
       </c>
       <c r="F110" s="37">
-        <f>SUM(F17:F109)</f>
+        <f t="shared" si="2"/>
         <v>357</v>
       </c>
       <c r="G110" s="37">
-        <f>SUM(G17:G109)</f>
+        <f t="shared" si="2"/>
         <v>345</v>
       </c>
       <c r="H110" s="37">
-        <f>SUM(H17:H109)</f>
+        <f t="shared" si="2"/>
         <v>331</v>
       </c>
       <c r="I110" s="37">
-        <f>SUM(I17:I109)</f>
+        <f t="shared" si="2"/>
         <v>324</v>
       </c>
       <c r="J110" s="37">
-        <f>SUM(J17:J109)</f>
+        <f t="shared" si="2"/>
         <v>313</v>
       </c>
       <c r="K110" s="37">
-        <f>SUM(K17:K109)</f>
+        <f t="shared" si="2"/>
         <v>303</v>
       </c>
       <c r="L110" s="37">
-        <f>SUM(L17:L109)</f>
+        <f t="shared" si="2"/>
         <v>267</v>
       </c>
       <c r="M110" s="37">
-        <f>SUM(M17:M109)</f>
+        <f t="shared" si="2"/>
         <v>267</v>
       </c>
       <c r="N110" s="37">
-        <f>SUM(N17:N109)</f>
+        <f t="shared" si="2"/>
         <v>228</v>
       </c>
       <c r="O110" s="37">
-        <f>SUM(O17:O109)</f>
+        <f t="shared" si="2"/>
         <v>227</v>
       </c>
       <c r="P110" s="37">
-        <f>SUM(P17:P109)</f>
+        <f t="shared" si="2"/>
         <v>219</v>
       </c>
       <c r="Q110" s="37">
-        <f>SUM(Q17:Q109)</f>
+        <f t="shared" si="2"/>
         <v>199</v>
       </c>
       <c r="R110" s="29">
-        <f>SUM(R17:R109)</f>
+        <f t="shared" si="2"/>
         <v>184</v>
       </c>
       <c r="S110" s="50">
-        <f>SUM(S17:S109)</f>
+        <f t="shared" si="2"/>
         <v>164</v>
       </c>
       <c r="T110" s="50">
-        <f>SUM(T17:T109)</f>
+        <f t="shared" si="2"/>
         <v>144</v>
       </c>
       <c r="U110" s="50">
-        <f>SUM(U17:U109)</f>
+        <f t="shared" si="2"/>
         <v>139</v>
       </c>
       <c r="V110" s="50">
-        <f>SUM(V17:V109)</f>
+        <f t="shared" si="2"/>
         <v>121</v>
       </c>
       <c r="W110" s="50">
-        <f>SUM(W17:W109)</f>
+        <f t="shared" si="2"/>
         <v>99</v>
       </c>
       <c r="X110" s="50">
-        <f>SUM(X17:X109)</f>
+        <f t="shared" si="2"/>
         <v>87</v>
       </c>
       <c r="Y110" s="50">
-        <f>SUM(Y17:Y109)</f>
+        <f t="shared" si="2"/>
         <v>65</v>
       </c>
       <c r="Z110" s="50">
-        <f>SUM(Z17:Z109)</f>
+        <f t="shared" si="2"/>
         <v>59</v>
       </c>
       <c r="AA110" s="50">
-        <f>SUM(AA17:AA109)</f>
+        <f t="shared" si="2"/>
         <v>51</v>
       </c>
       <c r="AB110" s="50">
-        <f>SUM(AB17:AB109)</f>
+        <f t="shared" si="2"/>
         <v>44</v>
       </c>
       <c r="AC110" s="50">
-        <f>SUM(AC17:AC109)</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="AD110" s="50">
-        <f>SUM(AD17:AD109)</f>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="AE110" s="50">
-        <f>SUM(AE17:AE109)</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="AF110" s="26">
@@ -31751,35 +31725,35 @@
         <v>46128</v>
       </c>
       <c r="G113" s="21">
-        <f t="shared" ref="G113" si="2">F113+1</f>
+        <f t="shared" ref="G113" si="3">F113+1</f>
         <v>46129</v>
       </c>
       <c r="H113" s="21">
-        <f t="shared" ref="H113" si="3">G113+1</f>
+        <f t="shared" ref="H113" si="4">G113+1</f>
         <v>46130</v>
       </c>
       <c r="I113" s="21">
-        <f t="shared" ref="I113" si="4">H113+1</f>
+        <f t="shared" ref="I113" si="5">H113+1</f>
         <v>46131</v>
       </c>
       <c r="J113" s="21">
-        <f t="shared" ref="J113" si="5">I113+1</f>
+        <f t="shared" ref="J113" si="6">I113+1</f>
         <v>46132</v>
       </c>
       <c r="K113" s="21">
-        <f t="shared" ref="K113" si="6">J113+1</f>
+        <f t="shared" ref="K113" si="7">J113+1</f>
         <v>46133</v>
       </c>
       <c r="L113" s="21">
-        <f t="shared" ref="L113" si="7">K113+1</f>
+        <f t="shared" ref="L113" si="8">K113+1</f>
         <v>46134</v>
       </c>
       <c r="M113" s="21">
-        <f t="shared" ref="M113" si="8">L113+1</f>
+        <f t="shared" ref="M113" si="9">L113+1</f>
         <v>46135</v>
       </c>
       <c r="N113" s="21">
-        <f t="shared" ref="N113" si="9">M113+1</f>
+        <f t="shared" ref="N113" si="10">M113+1</f>
         <v>46136</v>
       </c>
       <c r="O113" s="21">
@@ -31787,19 +31761,19 @@
         <v>46137</v>
       </c>
       <c r="P113" s="21">
-        <f t="shared" ref="P113" si="10">O113+1</f>
+        <f t="shared" ref="P113" si="11">O113+1</f>
         <v>46138</v>
       </c>
       <c r="Q113" s="21">
-        <f t="shared" ref="Q113" si="11">P113+1</f>
+        <f t="shared" ref="Q113" si="12">P113+1</f>
         <v>46139</v>
       </c>
       <c r="R113" s="21">
-        <f t="shared" ref="R113" si="12">Q113+1</f>
+        <f t="shared" ref="R113" si="13">Q113+1</f>
         <v>46140</v>
       </c>
       <c r="S113" s="21">
-        <f t="shared" ref="S113" si="13">R113+1</f>
+        <f t="shared" ref="S113" si="14">R113+1</f>
         <v>46141</v>
       </c>
       <c r="T113" s="21">
@@ -31807,11 +31781,11 @@
         <v>46142</v>
       </c>
       <c r="U113" s="21">
-        <f t="shared" ref="U113" si="14">T113+1</f>
+        <f t="shared" ref="U113" si="15">T113+1</f>
         <v>46143</v>
       </c>
       <c r="V113" s="21">
-        <f t="shared" ref="V113" si="15">U113+1</f>
+        <f t="shared" ref="V113" si="16">U113+1</f>
         <v>46144</v>
       </c>
       <c r="W113" s="21">
@@ -31819,47 +31793,47 @@
         <v>46145</v>
       </c>
       <c r="X113" s="21">
-        <f t="shared" ref="X113" si="16">W113+1</f>
+        <f t="shared" ref="X113" si="17">W113+1</f>
         <v>46146</v>
       </c>
       <c r="Y113" s="21">
-        <f t="shared" ref="Y113" si="17">X113+1</f>
+        <f t="shared" ref="Y113" si="18">X113+1</f>
         <v>46147</v>
       </c>
       <c r="Z113" s="21">
-        <f t="shared" ref="Z113" si="18">Y113+1</f>
+        <f t="shared" ref="Z113" si="19">Y113+1</f>
         <v>46148</v>
       </c>
       <c r="AA113" s="21">
-        <f t="shared" ref="AA113" si="19">Z113+1</f>
+        <f t="shared" ref="AA113" si="20">Z113+1</f>
         <v>46149</v>
       </c>
       <c r="AB113" s="21">
-        <f t="shared" ref="AB113" si="20">AA113+1</f>
+        <f t="shared" ref="AB113" si="21">AA113+1</f>
         <v>46150</v>
       </c>
       <c r="AC113" s="21">
-        <f t="shared" ref="AC113" si="21">AB113+1</f>
+        <f t="shared" ref="AC113" si="22">AB113+1</f>
         <v>46151</v>
       </c>
       <c r="AD113" s="21">
-        <f t="shared" ref="AD113" si="22">AC113+1</f>
+        <f t="shared" ref="AD113" si="23">AC113+1</f>
         <v>46152</v>
       </c>
       <c r="AE113" s="21">
-        <f t="shared" ref="AE113" si="23">AD113+1</f>
+        <f t="shared" ref="AE113" si="24">AD113+1</f>
         <v>46153</v>
       </c>
       <c r="AF113" s="21">
-        <f t="shared" ref="AF113" si="24">AE113+1</f>
+        <f t="shared" ref="AF113" si="25">AE113+1</f>
         <v>46154</v>
       </c>
     </row>
     <row r="114" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A114" s="109" t="s">
+      <c r="A114" s="134" t="s">
         <v>75</v>
       </c>
-      <c r="B114" s="110"/>
+      <c r="B114" s="135"/>
       <c r="C114" s="22" t="s">
         <v>25</v>
       </c>
@@ -31950,10 +31924,10 @@
       </c>
     </row>
     <row r="115" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A115" s="109" t="s">
+      <c r="A115" s="134" t="s">
         <v>26</v>
       </c>
-      <c r="B115" s="110"/>
+      <c r="B115" s="135"/>
       <c r="C115" s="27" t="s">
         <v>40</v>
       </c>
@@ -32044,10 +32018,10 @@
       </c>
     </row>
     <row r="116" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A116" s="109" t="s">
+      <c r="A116" s="134" t="s">
         <v>76</v>
       </c>
-      <c r="B116" s="110"/>
+      <c r="B116" s="135"/>
       <c r="C116" s="22" t="s">
         <v>25</v>
       </c>
@@ -32138,10 +32112,10 @@
       </c>
     </row>
     <row r="117" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A117" s="111" t="s">
+      <c r="A117" s="136" t="s">
         <v>28</v>
       </c>
-      <c r="B117" s="139"/>
+      <c r="B117" s="157"/>
       <c r="C117" s="27" t="s">
         <v>25</v>
       </c>
@@ -32232,7 +32206,7 @@
       </c>
     </row>
     <row r="118" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A118" s="140" t="s">
+      <c r="A118" s="158" t="s">
         <v>29</v>
       </c>
       <c r="B118" s="73" t="s">
@@ -32328,7 +32302,7 @@
       </c>
     </row>
     <row r="119" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A119" s="141"/>
+      <c r="A119" s="159"/>
       <c r="B119" s="73" t="s">
         <v>78</v>
       </c>
@@ -32422,7 +32396,7 @@
       </c>
     </row>
     <row r="120" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A120" s="141"/>
+      <c r="A120" s="159"/>
       <c r="B120" s="74" t="s">
         <v>79</v>
       </c>
@@ -32516,7 +32490,7 @@
       </c>
     </row>
     <row r="121" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A121" s="141"/>
+      <c r="A121" s="159"/>
       <c r="B121" s="75" t="s">
         <v>80</v>
       </c>
@@ -32607,7 +32581,7 @@
       </c>
     </row>
     <row r="122" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A122" s="141"/>
+      <c r="A122" s="159"/>
       <c r="B122" s="74" t="s">
         <v>81</v>
       </c>
@@ -32701,7 +32675,7 @@
       </c>
     </row>
     <row r="123" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A123" s="141"/>
+      <c r="A123" s="159"/>
       <c r="B123" s="74" t="s">
         <v>82</v>
       </c>
@@ -32795,7 +32769,7 @@
       </c>
     </row>
     <row r="124" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A124" s="141"/>
+      <c r="A124" s="159"/>
       <c r="B124" s="76" t="s">
         <v>83</v>
       </c>
@@ -32889,7 +32863,7 @@
       </c>
     </row>
     <row r="125" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A125" s="141"/>
+      <c r="A125" s="159"/>
       <c r="B125" s="76" t="s">
         <v>84</v>
       </c>
@@ -32983,7 +32957,7 @@
       </c>
     </row>
     <row r="126" spans="1:32" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A126" s="141"/>
+      <c r="A126" s="159"/>
       <c r="B126" s="76" t="s">
         <v>85</v>
       </c>
@@ -33077,7 +33051,7 @@
       </c>
     </row>
     <row r="127" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A127" s="141"/>
+      <c r="A127" s="159"/>
       <c r="B127" s="76" t="s">
         <v>86</v>
       </c>
@@ -33171,7 +33145,7 @@
       </c>
     </row>
     <row r="128" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A128" s="141"/>
+      <c r="A128" s="159"/>
       <c r="B128" s="76" t="s">
         <v>87</v>
       </c>
@@ -33265,7 +33239,7 @@
       </c>
     </row>
     <row r="129" spans="1:40" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A129" s="141"/>
+      <c r="A129" s="159"/>
       <c r="B129" s="76" t="s">
         <v>88</v>
       </c>
@@ -33358,8 +33332,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:40" s="154" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A130" s="141"/>
+    <row r="130" spans="1:40" s="114" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A130" s="159"/>
       <c r="B130" s="76" t="s">
         <v>107</v>
       </c>
@@ -33378,22 +33352,22 @@
       <c r="H130" s="24">
         <v>2</v>
       </c>
-      <c r="I130" s="163">
-        <v>1</v>
-      </c>
-      <c r="J130" s="144">
+      <c r="I130" s="119">
+        <v>1</v>
+      </c>
+      <c r="J130" s="105">
         <v>0</v>
       </c>
       <c r="K130" s="57">
         <v>0</v>
       </c>
-      <c r="L130" s="145">
-        <v>0</v>
-      </c>
-      <c r="M130" s="145">
-        <v>0</v>
-      </c>
-      <c r="N130" s="146">
+      <c r="L130" s="106">
+        <v>0</v>
+      </c>
+      <c r="M130" s="106">
+        <v>0</v>
+      </c>
+      <c r="N130" s="107">
         <v>0</v>
       </c>
       <c r="O130" s="38">
@@ -33450,17 +33424,17 @@
       <c r="AF130" s="38">
         <v>0</v>
       </c>
-      <c r="AG130" s="156"/>
-      <c r="AH130" s="156"/>
-      <c r="AI130" s="156"/>
-      <c r="AJ130" s="156"/>
-      <c r="AK130" s="156"/>
-      <c r="AL130" s="156"/>
-      <c r="AM130" s="156"/>
-      <c r="AN130" s="155"/>
-    </row>
-    <row r="131" spans="1:40" s="154" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A131" s="141"/>
+      <c r="AG130"/>
+      <c r="AH130"/>
+      <c r="AI130"/>
+      <c r="AJ130"/>
+      <c r="AK130"/>
+      <c r="AL130"/>
+      <c r="AM130"/>
+      <c r="AN130" s="115"/>
+    </row>
+    <row r="131" spans="1:40" s="114" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A131" s="159"/>
       <c r="B131" s="76" t="s">
         <v>108</v>
       </c>
@@ -33479,22 +33453,22 @@
       <c r="H131" s="24">
         <v>2</v>
       </c>
-      <c r="I131" s="163">
-        <v>1</v>
-      </c>
-      <c r="J131" s="144">
+      <c r="I131" s="119">
+        <v>1</v>
+      </c>
+      <c r="J131" s="105">
         <v>0</v>
       </c>
       <c r="K131" s="57">
         <v>0</v>
       </c>
-      <c r="L131" s="145">
-        <v>0</v>
-      </c>
-      <c r="M131" s="145">
-        <v>0</v>
-      </c>
-      <c r="N131" s="146">
+      <c r="L131" s="106">
+        <v>0</v>
+      </c>
+      <c r="M131" s="106">
+        <v>0</v>
+      </c>
+      <c r="N131" s="107">
         <v>0</v>
       </c>
       <c r="O131" s="38">
@@ -33551,17 +33525,17 @@
       <c r="AF131" s="38">
         <v>0</v>
       </c>
-      <c r="AG131" s="156"/>
-      <c r="AH131" s="156"/>
-      <c r="AI131" s="156"/>
-      <c r="AJ131" s="156"/>
-      <c r="AK131" s="156"/>
-      <c r="AL131" s="156"/>
-      <c r="AM131" s="156"/>
-      <c r="AN131" s="155"/>
+      <c r="AG131"/>
+      <c r="AH131"/>
+      <c r="AI131"/>
+      <c r="AJ131"/>
+      <c r="AK131"/>
+      <c r="AL131"/>
+      <c r="AM131"/>
+      <c r="AN131" s="115"/>
     </row>
     <row r="132" spans="1:40" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A132" s="142"/>
+      <c r="A132" s="160"/>
       <c r="B132" s="72" t="s">
         <v>32</v>
       </c>
@@ -33655,7 +33629,7 @@
       </c>
     </row>
     <row r="133" spans="1:40" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A133" s="132" t="s">
+      <c r="A133" s="141" t="s">
         <v>33</v>
       </c>
       <c r="B133" s="73" t="s">
@@ -33751,7 +33725,7 @@
       </c>
     </row>
     <row r="134" spans="1:40" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A134" s="133"/>
+      <c r="A134" s="142"/>
       <c r="B134" s="73" t="s">
         <v>78</v>
       </c>
@@ -33845,7 +33819,7 @@
       </c>
     </row>
     <row r="135" spans="1:40" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A135" s="133"/>
+      <c r="A135" s="142"/>
       <c r="B135" s="74" t="s">
         <v>79</v>
       </c>
@@ -33939,7 +33913,7 @@
       </c>
     </row>
     <row r="136" spans="1:40" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A136" s="133"/>
+      <c r="A136" s="142"/>
       <c r="B136" s="75" t="s">
         <v>80</v>
       </c>
@@ -34033,7 +34007,7 @@
       </c>
     </row>
     <row r="137" spans="1:40" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A137" s="133"/>
+      <c r="A137" s="142"/>
       <c r="B137" s="74" t="s">
         <v>81</v>
       </c>
@@ -34127,7 +34101,7 @@
       </c>
     </row>
     <row r="138" spans="1:40" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A138" s="133"/>
+      <c r="A138" s="142"/>
       <c r="B138" s="74" t="s">
         <v>82</v>
       </c>
@@ -34221,7 +34195,7 @@
       </c>
     </row>
     <row r="139" spans="1:40" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A139" s="133"/>
+      <c r="A139" s="142"/>
       <c r="B139" s="76" t="s">
         <v>83</v>
       </c>
@@ -34315,7 +34289,7 @@
       </c>
     </row>
     <row r="140" spans="1:40" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A140" s="133"/>
+      <c r="A140" s="142"/>
       <c r="B140" s="76" t="s">
         <v>84</v>
       </c>
@@ -34409,7 +34383,7 @@
       </c>
     </row>
     <row r="141" spans="1:40" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A141" s="133"/>
+      <c r="A141" s="142"/>
       <c r="B141" s="76" t="s">
         <v>85</v>
       </c>
@@ -34503,7 +34477,7 @@
       </c>
     </row>
     <row r="142" spans="1:40" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A142" s="133"/>
+      <c r="A142" s="142"/>
       <c r="B142" s="76" t="s">
         <v>86</v>
       </c>
@@ -34597,7 +34571,7 @@
       </c>
     </row>
     <row r="143" spans="1:40" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A143" s="133"/>
+      <c r="A143" s="142"/>
       <c r="B143" s="76" t="s">
         <v>87</v>
       </c>
@@ -34691,7 +34665,7 @@
       </c>
     </row>
     <row r="144" spans="1:40" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A144" s="133"/>
+      <c r="A144" s="142"/>
       <c r="B144" s="76" t="s">
         <v>88</v>
       </c>
@@ -34785,7 +34759,7 @@
       </c>
     </row>
     <row r="145" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A145" s="133"/>
+      <c r="A145" s="142"/>
       <c r="B145" s="76" t="s">
         <v>107</v>
       </c>
@@ -34879,7 +34853,7 @@
       </c>
     </row>
     <row r="146" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A146" s="133"/>
+      <c r="A146" s="142"/>
       <c r="B146" s="76" t="s">
         <v>108</v>
       </c>
@@ -34973,7 +34947,7 @@
       </c>
     </row>
     <row r="147" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A147" s="133"/>
+      <c r="A147" s="142"/>
       <c r="B147" s="73" t="s">
         <v>32</v>
       </c>
@@ -35067,7 +35041,7 @@
       </c>
     </row>
     <row r="148" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A148" s="134" t="s">
+      <c r="A148" s="130" t="s">
         <v>34</v>
       </c>
       <c r="B148" s="73" t="s">
@@ -35163,7 +35137,7 @@
       </c>
     </row>
     <row r="149" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A149" s="134"/>
+      <c r="A149" s="130"/>
       <c r="B149" s="73" t="s">
         <v>78</v>
       </c>
@@ -35257,7 +35231,7 @@
       </c>
     </row>
     <row r="150" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A150" s="134"/>
+      <c r="A150" s="130"/>
       <c r="B150" s="74" t="s">
         <v>79</v>
       </c>
@@ -35351,7 +35325,7 @@
       </c>
     </row>
     <row r="151" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A151" s="134"/>
+      <c r="A151" s="130"/>
       <c r="B151" s="75" t="s">
         <v>80</v>
       </c>
@@ -35445,7 +35419,7 @@
       </c>
     </row>
     <row r="152" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A152" s="134"/>
+      <c r="A152" s="130"/>
       <c r="B152" s="74" t="s">
         <v>81</v>
       </c>
@@ -35539,7 +35513,7 @@
       </c>
     </row>
     <row r="153" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A153" s="134"/>
+      <c r="A153" s="130"/>
       <c r="B153" s="74" t="s">
         <v>82</v>
       </c>
@@ -35633,7 +35607,7 @@
       </c>
     </row>
     <row r="154" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A154" s="134"/>
+      <c r="A154" s="130"/>
       <c r="B154" s="76" t="s">
         <v>83</v>
       </c>
@@ -35727,7 +35701,7 @@
       </c>
     </row>
     <row r="155" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A155" s="134"/>
+      <c r="A155" s="130"/>
       <c r="B155" s="76" t="s">
         <v>84</v>
       </c>
@@ -35821,7 +35795,7 @@
       </c>
     </row>
     <row r="156" spans="1:32" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A156" s="134"/>
+      <c r="A156" s="130"/>
       <c r="B156" s="76" t="s">
         <v>85</v>
       </c>
@@ -35915,7 +35889,7 @@
       </c>
     </row>
     <row r="157" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A157" s="134"/>
+      <c r="A157" s="130"/>
       <c r="B157" s="76" t="s">
         <v>86</v>
       </c>
@@ -36009,7 +35983,7 @@
       </c>
     </row>
     <row r="158" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A158" s="134"/>
+      <c r="A158" s="130"/>
       <c r="B158" s="76" t="s">
         <v>87</v>
       </c>
@@ -36103,7 +36077,7 @@
       </c>
     </row>
     <row r="159" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A159" s="134"/>
+      <c r="A159" s="130"/>
       <c r="B159" s="76" t="s">
         <v>88</v>
       </c>
@@ -36197,7 +36171,7 @@
       </c>
     </row>
     <row r="160" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A160" s="134"/>
+      <c r="A160" s="130"/>
       <c r="B160" s="76" t="s">
         <v>107</v>
       </c>
@@ -36290,7 +36264,7 @@
       </c>
     </row>
     <row r="161" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A161" s="134"/>
+      <c r="A161" s="130"/>
       <c r="B161" s="76" t="s">
         <v>108</v>
       </c>
@@ -36383,7 +36357,7 @@
       </c>
     </row>
     <row r="162" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A162" s="134"/>
+      <c r="A162" s="130"/>
       <c r="B162" s="73" t="s">
         <v>91</v>
       </c>
@@ -36477,7 +36451,7 @@
       </c>
     </row>
     <row r="163" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A163" s="134" t="s">
+      <c r="A163" s="130" t="s">
         <v>35</v>
       </c>
       <c r="B163" s="73" t="s">
@@ -36573,7 +36547,7 @@
       </c>
     </row>
     <row r="164" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A164" s="134"/>
+      <c r="A164" s="130"/>
       <c r="B164" s="73" t="s">
         <v>78</v>
       </c>
@@ -36667,7 +36641,7 @@
       </c>
     </row>
     <row r="165" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A165" s="134"/>
+      <c r="A165" s="130"/>
       <c r="B165" s="74" t="s">
         <v>79</v>
       </c>
@@ -36761,7 +36735,7 @@
       </c>
     </row>
     <row r="166" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A166" s="134"/>
+      <c r="A166" s="130"/>
       <c r="B166" s="75" t="s">
         <v>80</v>
       </c>
@@ -36855,7 +36829,7 @@
       </c>
     </row>
     <row r="167" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A167" s="134"/>
+      <c r="A167" s="130"/>
       <c r="B167" s="74" t="s">
         <v>81</v>
       </c>
@@ -36949,7 +36923,7 @@
       </c>
     </row>
     <row r="168" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A168" s="134"/>
+      <c r="A168" s="130"/>
       <c r="B168" s="74" t="s">
         <v>82</v>
       </c>
@@ -37043,7 +37017,7 @@
       </c>
     </row>
     <row r="169" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A169" s="134"/>
+      <c r="A169" s="130"/>
       <c r="B169" s="76" t="s">
         <v>83</v>
       </c>
@@ -37137,7 +37111,7 @@
       </c>
     </row>
     <row r="170" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A170" s="134"/>
+      <c r="A170" s="130"/>
       <c r="B170" s="76" t="s">
         <v>84</v>
       </c>
@@ -37231,7 +37205,7 @@
       </c>
     </row>
     <row r="171" spans="1:32" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A171" s="134"/>
+      <c r="A171" s="130"/>
       <c r="B171" s="76" t="s">
         <v>85</v>
       </c>
@@ -37325,7 +37299,7 @@
       </c>
     </row>
     <row r="172" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A172" s="134"/>
+      <c r="A172" s="130"/>
       <c r="B172" s="76" t="s">
         <v>86</v>
       </c>
@@ -37419,7 +37393,7 @@
       </c>
     </row>
     <row r="173" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A173" s="134"/>
+      <c r="A173" s="130"/>
       <c r="B173" s="76" t="s">
         <v>87</v>
       </c>
@@ -37513,7 +37487,7 @@
       </c>
     </row>
     <row r="174" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A174" s="134"/>
+      <c r="A174" s="130"/>
       <c r="B174" s="76" t="s">
         <v>88</v>
       </c>
@@ -37607,7 +37581,7 @@
       </c>
     </row>
     <row r="175" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A175" s="134"/>
+      <c r="A175" s="130"/>
       <c r="B175" s="76" t="s">
         <v>107</v>
       </c>
@@ -37701,7 +37675,7 @@
       </c>
     </row>
     <row r="176" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A176" s="134"/>
+      <c r="A176" s="130"/>
       <c r="B176" s="76" t="s">
         <v>108</v>
       </c>
@@ -37795,7 +37769,7 @@
       </c>
     </row>
     <row r="177" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A177" s="134" t="s">
+      <c r="A177" s="130" t="s">
         <v>36</v>
       </c>
       <c r="B177" s="73" t="s">
@@ -37891,7 +37865,7 @@
       </c>
     </row>
     <row r="178" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A178" s="134"/>
+      <c r="A178" s="130"/>
       <c r="B178" s="73" t="s">
         <v>78</v>
       </c>
@@ -37985,7 +37959,7 @@
       </c>
     </row>
     <row r="179" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A179" s="134"/>
+      <c r="A179" s="130"/>
       <c r="B179" s="74" t="s">
         <v>79</v>
       </c>
@@ -38079,7 +38053,7 @@
       </c>
     </row>
     <row r="180" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A180" s="134"/>
+      <c r="A180" s="130"/>
       <c r="B180" s="75" t="s">
         <v>80</v>
       </c>
@@ -38173,7 +38147,7 @@
       </c>
     </row>
     <row r="181" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A181" s="134"/>
+      <c r="A181" s="130"/>
       <c r="B181" s="74" t="s">
         <v>81</v>
       </c>
@@ -38267,7 +38241,7 @@
       </c>
     </row>
     <row r="182" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A182" s="134"/>
+      <c r="A182" s="130"/>
       <c r="B182" s="74" t="s">
         <v>82</v>
       </c>
@@ -38361,7 +38335,7 @@
       </c>
     </row>
     <row r="183" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A183" s="134"/>
+      <c r="A183" s="130"/>
       <c r="B183" s="76" t="s">
         <v>83</v>
       </c>
@@ -38455,7 +38429,7 @@
       </c>
     </row>
     <row r="184" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A184" s="134"/>
+      <c r="A184" s="130"/>
       <c r="B184" s="76" t="s">
         <v>84</v>
       </c>
@@ -38549,7 +38523,7 @@
       </c>
     </row>
     <row r="185" spans="1:32" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A185" s="134"/>
+      <c r="A185" s="130"/>
       <c r="B185" s="76" t="s">
         <v>85</v>
       </c>
@@ -38643,7 +38617,7 @@
       </c>
     </row>
     <row r="186" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A186" s="134"/>
+      <c r="A186" s="130"/>
       <c r="B186" s="76" t="s">
         <v>86</v>
       </c>
@@ -38737,7 +38711,7 @@
       </c>
     </row>
     <row r="187" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A187" s="134"/>
+      <c r="A187" s="130"/>
       <c r="B187" s="76" t="s">
         <v>87</v>
       </c>
@@ -38831,7 +38805,7 @@
       </c>
     </row>
     <row r="188" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A188" s="134"/>
+      <c r="A188" s="130"/>
       <c r="B188" s="76" t="s">
         <v>88</v>
       </c>
@@ -38925,7 +38899,7 @@
       </c>
     </row>
     <row r="189" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A189" s="134"/>
+      <c r="A189" s="130"/>
       <c r="B189" s="76" t="s">
         <v>107</v>
       </c>
@@ -39018,83 +38992,83 @@
       </c>
     </row>
     <row r="190" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A190" s="134"/>
+      <c r="A190" s="130"/>
       <c r="B190" s="76" t="s">
         <v>108</v>
       </c>
       <c r="C190" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="D190" s="159">
-        <v>2</v>
-      </c>
-      <c r="F190" s="159">
-        <v>2</v>
-      </c>
-      <c r="G190" s="159">
-        <v>2</v>
-      </c>
-      <c r="H190" s="159">
-        <v>2</v>
-      </c>
-      <c r="I190" s="159">
-        <v>2</v>
-      </c>
-      <c r="J190" s="159">
-        <v>2</v>
-      </c>
-      <c r="K190" s="159">
-        <v>2</v>
-      </c>
-      <c r="L190" s="159">
-        <v>2</v>
-      </c>
-      <c r="M190" s="159">
-        <v>2</v>
-      </c>
-      <c r="N190" s="159">
-        <v>2</v>
-      </c>
-      <c r="O190" s="159">
-        <v>2</v>
-      </c>
-      <c r="P190" s="159">
-        <v>2</v>
-      </c>
-      <c r="Q190" s="159">
-        <v>2</v>
-      </c>
-      <c r="R190" s="159">
-        <v>2</v>
-      </c>
-      <c r="S190" s="159">
-        <v>2</v>
-      </c>
-      <c r="T190" s="159">
-        <v>2</v>
-      </c>
-      <c r="U190" s="159">
-        <v>2</v>
-      </c>
-      <c r="V190" s="159">
-        <v>2</v>
-      </c>
-      <c r="W190" s="159">
-        <v>2</v>
-      </c>
-      <c r="X190" s="159">
-        <v>2</v>
-      </c>
-      <c r="Y190" s="159">
-        <v>2</v>
-      </c>
-      <c r="Z190" s="159">
-        <v>2</v>
-      </c>
-      <c r="AA190" s="159">
-        <v>2</v>
-      </c>
-      <c r="AB190" s="159">
+      <c r="D190" s="24">
+        <v>2</v>
+      </c>
+      <c r="F190" s="24">
+        <v>2</v>
+      </c>
+      <c r="G190" s="24">
+        <v>2</v>
+      </c>
+      <c r="H190" s="24">
+        <v>2</v>
+      </c>
+      <c r="I190" s="24">
+        <v>2</v>
+      </c>
+      <c r="J190" s="24">
+        <v>2</v>
+      </c>
+      <c r="K190" s="24">
+        <v>2</v>
+      </c>
+      <c r="L190" s="24">
+        <v>2</v>
+      </c>
+      <c r="M190" s="24">
+        <v>2</v>
+      </c>
+      <c r="N190" s="24">
+        <v>2</v>
+      </c>
+      <c r="O190" s="24">
+        <v>2</v>
+      </c>
+      <c r="P190" s="24">
+        <v>2</v>
+      </c>
+      <c r="Q190" s="24">
+        <v>2</v>
+      </c>
+      <c r="R190" s="24">
+        <v>2</v>
+      </c>
+      <c r="S190" s="24">
+        <v>2</v>
+      </c>
+      <c r="T190" s="24">
+        <v>2</v>
+      </c>
+      <c r="U190" s="24">
+        <v>2</v>
+      </c>
+      <c r="V190" s="24">
+        <v>2</v>
+      </c>
+      <c r="W190" s="24">
+        <v>2</v>
+      </c>
+      <c r="X190" s="24">
+        <v>2</v>
+      </c>
+      <c r="Y190" s="24">
+        <v>2</v>
+      </c>
+      <c r="Z190" s="24">
+        <v>2</v>
+      </c>
+      <c r="AA190" s="24">
+        <v>2</v>
+      </c>
+      <c r="AB190" s="24">
         <v>2</v>
       </c>
       <c r="AC190" s="25">
@@ -39111,7 +39085,7 @@
       </c>
     </row>
     <row r="191" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A191" s="134" t="s">
+      <c r="A191" s="130" t="s">
         <v>37</v>
       </c>
       <c r="B191" s="73" t="s">
@@ -39207,7 +39181,7 @@
       </c>
     </row>
     <row r="192" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A192" s="134"/>
+      <c r="A192" s="130"/>
       <c r="B192" s="73" t="s">
         <v>78</v>
       </c>
@@ -39301,7 +39275,7 @@
       </c>
     </row>
     <row r="193" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A193" s="134"/>
+      <c r="A193" s="130"/>
       <c r="B193" s="74" t="s">
         <v>79</v>
       </c>
@@ -39395,7 +39369,7 @@
       </c>
     </row>
     <row r="194" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A194" s="134"/>
+      <c r="A194" s="130"/>
       <c r="B194" s="75" t="s">
         <v>80</v>
       </c>
@@ -39489,7 +39463,7 @@
       </c>
     </row>
     <row r="195" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A195" s="134"/>
+      <c r="A195" s="130"/>
       <c r="B195" s="74" t="s">
         <v>81</v>
       </c>
@@ -39583,7 +39557,7 @@
       </c>
     </row>
     <row r="196" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A196" s="134"/>
+      <c r="A196" s="130"/>
       <c r="B196" s="74" t="s">
         <v>82</v>
       </c>
@@ -39677,7 +39651,7 @@
       </c>
     </row>
     <row r="197" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A197" s="134"/>
+      <c r="A197" s="130"/>
       <c r="B197" s="76" t="s">
         <v>83</v>
       </c>
@@ -39771,7 +39745,7 @@
       </c>
     </row>
     <row r="198" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A198" s="134"/>
+      <c r="A198" s="130"/>
       <c r="B198" s="76" t="s">
         <v>84</v>
       </c>
@@ -39865,7 +39839,7 @@
       </c>
     </row>
     <row r="199" spans="1:32" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A199" s="134"/>
+      <c r="A199" s="130"/>
       <c r="B199" s="76" t="s">
         <v>85</v>
       </c>
@@ -39959,7 +39933,7 @@
       </c>
     </row>
     <row r="200" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A200" s="134"/>
+      <c r="A200" s="130"/>
       <c r="B200" s="76" t="s">
         <v>86</v>
       </c>
@@ -40053,7 +40027,7 @@
       </c>
     </row>
     <row r="201" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A201" s="134"/>
+      <c r="A201" s="130"/>
       <c r="B201" s="76" t="s">
         <v>87</v>
       </c>
@@ -40147,7 +40121,7 @@
       </c>
     </row>
     <row r="202" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A202" s="132"/>
+      <c r="A202" s="141"/>
       <c r="B202" s="76" t="s">
         <v>88</v>
       </c>
@@ -40241,8 +40215,8 @@
       </c>
     </row>
     <row r="203" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A203" s="158"/>
-      <c r="B203" s="153" t="s">
+      <c r="A203" s="54"/>
+      <c r="B203" s="113" t="s">
         <v>107</v>
       </c>
       <c r="C203" s="24" t="s">
@@ -40334,89 +40308,89 @@
       </c>
     </row>
     <row r="204" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A204" s="158"/>
-      <c r="B204" s="164" t="s">
+      <c r="A204" s="54"/>
+      <c r="B204" s="120" t="s">
         <v>108</v>
       </c>
       <c r="C204" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="D204" s="160">
-        <v>1</v>
-      </c>
-      <c r="F204" s="160">
-        <v>1</v>
-      </c>
-      <c r="G204" s="160">
-        <v>1</v>
-      </c>
-      <c r="H204" s="160">
-        <v>1</v>
-      </c>
-      <c r="I204" s="160">
-        <v>1</v>
-      </c>
-      <c r="J204" s="160">
-        <v>1</v>
-      </c>
-      <c r="K204" s="160">
-        <v>1</v>
-      </c>
-      <c r="L204" s="160">
-        <v>1</v>
-      </c>
-      <c r="M204" s="160">
-        <v>1</v>
-      </c>
-      <c r="N204" s="160">
-        <v>1</v>
-      </c>
-      <c r="O204" s="160">
-        <v>1</v>
-      </c>
-      <c r="P204" s="160">
-        <v>1</v>
-      </c>
-      <c r="Q204" s="160">
-        <v>1</v>
-      </c>
-      <c r="R204" s="160">
-        <v>1</v>
-      </c>
-      <c r="S204" s="160">
-        <v>1</v>
-      </c>
-      <c r="T204" s="160">
-        <v>1</v>
-      </c>
-      <c r="U204" s="160">
-        <v>1</v>
-      </c>
-      <c r="V204" s="160">
-        <v>1</v>
-      </c>
-      <c r="W204" s="160">
-        <v>1</v>
-      </c>
-      <c r="X204" s="160">
-        <v>1</v>
-      </c>
-      <c r="Y204" s="160">
-        <v>1</v>
-      </c>
-      <c r="Z204" s="160">
-        <v>1</v>
-      </c>
-      <c r="AA204" s="160">
-        <v>1</v>
-      </c>
-      <c r="AB204" s="160">
-        <v>1</v>
-      </c>
-      <c r="AC204" s="160">
-        <v>1</v>
-      </c>
-      <c r="AD204" s="160">
+      <c r="D204" s="103">
+        <v>1</v>
+      </c>
+      <c r="F204" s="103">
+        <v>1</v>
+      </c>
+      <c r="G204" s="103">
+        <v>1</v>
+      </c>
+      <c r="H204" s="103">
+        <v>1</v>
+      </c>
+      <c r="I204" s="103">
+        <v>1</v>
+      </c>
+      <c r="J204" s="103">
+        <v>1</v>
+      </c>
+      <c r="K204" s="103">
+        <v>1</v>
+      </c>
+      <c r="L204" s="103">
+        <v>1</v>
+      </c>
+      <c r="M204" s="103">
+        <v>1</v>
+      </c>
+      <c r="N204" s="103">
+        <v>1</v>
+      </c>
+      <c r="O204" s="103">
+        <v>1</v>
+      </c>
+      <c r="P204" s="103">
+        <v>1</v>
+      </c>
+      <c r="Q204" s="103">
+        <v>1</v>
+      </c>
+      <c r="R204" s="103">
+        <v>1</v>
+      </c>
+      <c r="S204" s="103">
+        <v>1</v>
+      </c>
+      <c r="T204" s="103">
+        <v>1</v>
+      </c>
+      <c r="U204" s="103">
+        <v>1</v>
+      </c>
+      <c r="V204" s="103">
+        <v>1</v>
+      </c>
+      <c r="W204" s="103">
+        <v>1</v>
+      </c>
+      <c r="X204" s="103">
+        <v>1</v>
+      </c>
+      <c r="Y204" s="103">
+        <v>1</v>
+      </c>
+      <c r="Z204" s="103">
+        <v>1</v>
+      </c>
+      <c r="AA204" s="103">
+        <v>1</v>
+      </c>
+      <c r="AB204" s="103">
+        <v>1</v>
+      </c>
+      <c r="AC204" s="103">
+        <v>1</v>
+      </c>
+      <c r="AD204" s="103">
         <v>1</v>
       </c>
       <c r="AE204" s="25">
@@ -40427,10 +40401,10 @@
       </c>
     </row>
     <row r="205" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A205" s="135" t="s">
+      <c r="A205" s="131" t="s">
         <v>89</v>
       </c>
-      <c r="B205" s="135"/>
+      <c r="B205" s="131"/>
       <c r="C205" s="44" t="s">
         <v>25</v>
       </c>
@@ -40521,10 +40495,10 @@
       </c>
     </row>
     <row r="206" spans="1:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A206" s="136" t="s">
+      <c r="A206" s="132" t="s">
         <v>90</v>
       </c>
-      <c r="B206" s="137"/>
+      <c r="B206" s="133"/>
       <c r="C206" s="47" t="s">
         <v>25</v>
       </c>
@@ -40626,107 +40600,107 @@
       </c>
       <c r="E207" s="46"/>
       <c r="F207" s="37">
-        <f>SUM(F114:F206)</f>
+        <f t="shared" ref="F207:AE207" si="26">SUM(F114:F206)</f>
         <v>357</v>
       </c>
       <c r="G207" s="37">
-        <f>SUM(G114:G206)</f>
+        <f t="shared" si="26"/>
         <v>347</v>
       </c>
       <c r="H207" s="37">
-        <f>SUM(H114:H206)</f>
+        <f t="shared" si="26"/>
         <v>335</v>
       </c>
       <c r="I207" s="37">
-        <f>SUM(I114:I206)</f>
+        <f t="shared" si="26"/>
         <v>322</v>
       </c>
       <c r="J207" s="37">
-        <f>SUM(J114:J206)</f>
+        <f t="shared" si="26"/>
         <v>310</v>
       </c>
       <c r="K207" s="37">
-        <f>SUM(K114:K206)</f>
+        <f t="shared" si="26"/>
         <v>308</v>
       </c>
       <c r="L207" s="37">
-        <f>SUM(L114:L206)</f>
+        <f t="shared" si="26"/>
         <v>267</v>
       </c>
       <c r="M207" s="37">
-        <f>SUM(M114:M206)</f>
+        <f t="shared" si="26"/>
         <v>269</v>
       </c>
       <c r="N207" s="37">
-        <f>SUM(N114:N206)</f>
+        <f t="shared" si="26"/>
         <v>228</v>
       </c>
       <c r="O207" s="37">
-        <f>SUM(O114:O206)</f>
+        <f t="shared" si="26"/>
         <v>227</v>
       </c>
       <c r="P207" s="37">
-        <f>SUM(P114:P206)</f>
+        <f t="shared" si="26"/>
         <v>224</v>
       </c>
       <c r="Q207" s="37">
-        <f>SUM(Q114:Q206)</f>
+        <f t="shared" si="26"/>
         <v>199</v>
       </c>
       <c r="R207" s="29">
-        <f>SUM(R114:R206)</f>
+        <f t="shared" si="26"/>
         <v>184</v>
       </c>
       <c r="S207" s="50">
-        <f>SUM(S114:S206)</f>
+        <f t="shared" si="26"/>
         <v>164</v>
       </c>
       <c r="T207" s="50">
-        <f>SUM(T114:T206)</f>
+        <f t="shared" si="26"/>
         <v>142</v>
       </c>
       <c r="U207" s="50">
-        <f>SUM(U114:U206)</f>
+        <f t="shared" si="26"/>
         <v>137</v>
       </c>
       <c r="V207" s="50">
-        <f>SUM(V114:V206)</f>
+        <f t="shared" si="26"/>
         <v>118</v>
       </c>
       <c r="W207" s="50">
-        <f>SUM(W114:W206)</f>
+        <f t="shared" si="26"/>
         <v>99</v>
       </c>
       <c r="X207" s="50">
-        <f>SUM(X114:X206)</f>
+        <f t="shared" si="26"/>
         <v>88</v>
       </c>
       <c r="Y207" s="50">
-        <f>SUM(Y114:Y206)</f>
+        <f t="shared" si="26"/>
         <v>70</v>
       </c>
       <c r="Z207" s="50">
-        <f>SUM(Z114:Z206)</f>
+        <f t="shared" si="26"/>
         <v>61</v>
       </c>
       <c r="AA207" s="50">
-        <f>SUM(AA114:AA206)</f>
+        <f t="shared" si="26"/>
         <v>55</v>
       </c>
       <c r="AB207" s="50">
-        <f>SUM(AB114:AB206)</f>
+        <f t="shared" si="26"/>
         <v>45</v>
       </c>
       <c r="AC207" s="50">
-        <f>SUM(AC114:AC206)</f>
+        <f t="shared" si="26"/>
         <v>27</v>
       </c>
       <c r="AD207" s="50">
-        <f>SUM(AD114:AD206)</f>
+        <f t="shared" si="26"/>
         <v>19</v>
       </c>
       <c r="AE207" s="50">
-        <f>SUM(AE114:AE206)</f>
+        <f t="shared" si="26"/>
         <v>8</v>
       </c>
       <c r="AF207" s="26">
@@ -40734,36 +40708,36 @@
       </c>
     </row>
     <row r="210" spans="4:32" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="D210" s="138" t="s">
+      <c r="D210" s="129" t="s">
         <v>103</v>
       </c>
-      <c r="E210" s="138"/>
-      <c r="F210" s="138"/>
-      <c r="G210" s="138"/>
-      <c r="H210" s="138"/>
-      <c r="I210" s="138"/>
-      <c r="J210" s="138"/>
-      <c r="K210" s="138"/>
-      <c r="L210" s="138"/>
-      <c r="M210" s="138"/>
-      <c r="N210" s="138"/>
-      <c r="O210" s="138"/>
-      <c r="P210" s="138"/>
-      <c r="Q210" s="138"/>
-      <c r="R210" s="138"/>
-      <c r="S210" s="138"/>
-      <c r="T210" s="138"/>
-      <c r="U210" s="138"/>
-      <c r="V210" s="138"/>
-      <c r="W210" s="138"/>
-      <c r="X210" s="138"/>
-      <c r="Y210" s="138"/>
-      <c r="Z210" s="138"/>
-      <c r="AA210" s="138"/>
-      <c r="AB210" s="138"/>
-      <c r="AC210" s="138"/>
-      <c r="AD210" s="138"/>
-      <c r="AE210" s="138"/>
+      <c r="E210" s="129"/>
+      <c r="F210" s="129"/>
+      <c r="G210" s="129"/>
+      <c r="H210" s="129"/>
+      <c r="I210" s="129"/>
+      <c r="J210" s="129"/>
+      <c r="K210" s="129"/>
+      <c r="L210" s="129"/>
+      <c r="M210" s="129"/>
+      <c r="N210" s="129"/>
+      <c r="O210" s="129"/>
+      <c r="P210" s="129"/>
+      <c r="Q210" s="129"/>
+      <c r="R210" s="129"/>
+      <c r="S210" s="129"/>
+      <c r="T210" s="129"/>
+      <c r="U210" s="129"/>
+      <c r="V210" s="129"/>
+      <c r="W210" s="129"/>
+      <c r="X210" s="129"/>
+      <c r="Y210" s="129"/>
+      <c r="Z210" s="129"/>
+      <c r="AA210" s="129"/>
+      <c r="AB210" s="129"/>
+      <c r="AC210" s="129"/>
+      <c r="AD210" s="129"/>
+      <c r="AE210" s="129"/>
     </row>
     <row r="211" spans="4:32" ht="52.2" x14ac:dyDescent="0.3">
       <c r="D211" s="65"/>
@@ -40772,35 +40746,35 @@
         <v>46128</v>
       </c>
       <c r="G211" s="21">
-        <f t="shared" ref="G211" si="25">F211+1</f>
+        <f t="shared" ref="G211" si="27">F211+1</f>
         <v>46129</v>
       </c>
       <c r="H211" s="21">
-        <f t="shared" ref="H211" si="26">G211+1</f>
+        <f t="shared" ref="H211" si="28">G211+1</f>
         <v>46130</v>
       </c>
       <c r="I211" s="21">
-        <f t="shared" ref="I211" si="27">H211+1</f>
+        <f t="shared" ref="I211" si="29">H211+1</f>
         <v>46131</v>
       </c>
       <c r="J211" s="21">
-        <f t="shared" ref="J211" si="28">I211+1</f>
+        <f t="shared" ref="J211" si="30">I211+1</f>
         <v>46132</v>
       </c>
       <c r="K211" s="21">
-        <f t="shared" ref="K211" si="29">J211+1</f>
+        <f t="shared" ref="K211" si="31">J211+1</f>
         <v>46133</v>
       </c>
       <c r="L211" s="21">
-        <f t="shared" ref="L211" si="30">K211+1</f>
+        <f t="shared" ref="L211" si="32">K211+1</f>
         <v>46134</v>
       </c>
       <c r="M211" s="21">
-        <f t="shared" ref="M211" si="31">L211+1</f>
+        <f t="shared" ref="M211" si="33">L211+1</f>
         <v>46135</v>
       </c>
       <c r="N211" s="21">
-        <f t="shared" ref="N211" si="32">M211+1</f>
+        <f t="shared" ref="N211" si="34">M211+1</f>
         <v>46136</v>
       </c>
       <c r="O211" s="21">
@@ -40808,19 +40782,19 @@
         <v>46137</v>
       </c>
       <c r="P211" s="21">
-        <f t="shared" ref="P211" si="33">O211+1</f>
+        <f t="shared" ref="P211" si="35">O211+1</f>
         <v>46138</v>
       </c>
       <c r="Q211" s="21">
-        <f t="shared" ref="Q211" si="34">P211+1</f>
+        <f t="shared" ref="Q211" si="36">P211+1</f>
         <v>46139</v>
       </c>
       <c r="R211" s="21">
-        <f t="shared" ref="R211" si="35">Q211+1</f>
+        <f t="shared" ref="R211" si="37">Q211+1</f>
         <v>46140</v>
       </c>
       <c r="S211" s="21">
-        <f t="shared" ref="S211" si="36">R211+1</f>
+        <f t="shared" ref="S211" si="38">R211+1</f>
         <v>46141</v>
       </c>
       <c r="T211" s="21">
@@ -40828,11 +40802,11 @@
         <v>46142</v>
       </c>
       <c r="U211" s="21">
-        <f t="shared" ref="U211" si="37">T211+1</f>
+        <f t="shared" ref="U211" si="39">T211+1</f>
         <v>46143</v>
       </c>
       <c r="V211" s="21">
-        <f t="shared" ref="V211" si="38">U211+1</f>
+        <f t="shared" ref="V211" si="40">U211+1</f>
         <v>46144</v>
       </c>
       <c r="W211" s="21">
@@ -40840,39 +40814,39 @@
         <v>46145</v>
       </c>
       <c r="X211" s="21">
-        <f t="shared" ref="X211" si="39">W211+1</f>
+        <f t="shared" ref="X211" si="41">W211+1</f>
         <v>46146</v>
       </c>
       <c r="Y211" s="21">
-        <f t="shared" ref="Y211" si="40">X211+1</f>
+        <f t="shared" ref="Y211" si="42">X211+1</f>
         <v>46147</v>
       </c>
       <c r="Z211" s="21">
-        <f t="shared" ref="Z211" si="41">Y211+1</f>
+        <f t="shared" ref="Z211" si="43">Y211+1</f>
         <v>46148</v>
       </c>
       <c r="AA211" s="21">
-        <f t="shared" ref="AA211" si="42">Z211+1</f>
+        <f t="shared" ref="AA211" si="44">Z211+1</f>
         <v>46149</v>
       </c>
       <c r="AB211" s="21">
-        <f t="shared" ref="AB211" si="43">AA211+1</f>
+        <f t="shared" ref="AB211" si="45">AA211+1</f>
         <v>46150</v>
       </c>
       <c r="AC211" s="21">
-        <f t="shared" ref="AC211" si="44">AB211+1</f>
+        <f t="shared" ref="AC211" si="46">AB211+1</f>
         <v>46151</v>
       </c>
       <c r="AD211" s="21">
-        <f t="shared" ref="AD211" si="45">AC211+1</f>
+        <f t="shared" ref="AD211" si="47">AC211+1</f>
         <v>46152</v>
       </c>
       <c r="AE211" s="21">
-        <f t="shared" ref="AE211" si="46">AD211+1</f>
+        <f t="shared" ref="AE211" si="48">AD211+1</f>
         <v>46153</v>
       </c>
       <c r="AF211" s="21">
-        <f t="shared" ref="AF211" si="47">AE211+1</f>
+        <f t="shared" ref="AF211" si="49">AE211+1</f>
         <v>46154</v>
       </c>
     </row>
@@ -40881,115 +40855,115 @@
         <v>9</v>
       </c>
       <c r="E212" s="37">
-        <f>E110</f>
+        <f t="shared" ref="E212:AF212" si="50">E110</f>
         <v>360</v>
       </c>
       <c r="F212" s="37">
-        <f>F110</f>
+        <f t="shared" si="50"/>
         <v>357</v>
       </c>
       <c r="G212" s="37">
-        <f>G110</f>
+        <f t="shared" si="50"/>
         <v>345</v>
       </c>
       <c r="H212" s="37">
-        <f>H110</f>
+        <f t="shared" si="50"/>
         <v>331</v>
       </c>
       <c r="I212" s="37">
-        <f>I110</f>
+        <f t="shared" si="50"/>
         <v>324</v>
       </c>
       <c r="J212" s="37">
-        <f>J110</f>
+        <f t="shared" si="50"/>
         <v>313</v>
       </c>
       <c r="K212" s="37">
-        <f>K110</f>
+        <f t="shared" si="50"/>
         <v>303</v>
       </c>
       <c r="L212" s="37">
-        <f>L110</f>
+        <f t="shared" si="50"/>
         <v>267</v>
       </c>
       <c r="M212" s="37">
-        <f>M110</f>
+        <f t="shared" si="50"/>
         <v>267</v>
       </c>
       <c r="N212" s="37">
-        <f>N110</f>
+        <f t="shared" si="50"/>
         <v>228</v>
       </c>
       <c r="O212" s="37">
-        <f>O110</f>
+        <f t="shared" si="50"/>
         <v>227</v>
       </c>
       <c r="P212" s="37">
-        <f>P110</f>
+        <f t="shared" si="50"/>
         <v>219</v>
       </c>
       <c r="Q212" s="37">
-        <f>Q110</f>
+        <f t="shared" si="50"/>
         <v>199</v>
       </c>
       <c r="R212" s="37">
-        <f>R110</f>
+        <f t="shared" si="50"/>
         <v>184</v>
       </c>
       <c r="S212" s="37">
-        <f>S110</f>
+        <f t="shared" si="50"/>
         <v>164</v>
       </c>
       <c r="T212" s="37">
-        <f>T110</f>
+        <f t="shared" si="50"/>
         <v>144</v>
       </c>
       <c r="U212" s="37">
-        <f>U110</f>
+        <f t="shared" si="50"/>
         <v>139</v>
       </c>
       <c r="V212" s="37">
-        <f>V110</f>
+        <f t="shared" si="50"/>
         <v>121</v>
       </c>
       <c r="W212" s="37">
-        <f>W110</f>
+        <f t="shared" si="50"/>
         <v>99</v>
       </c>
       <c r="X212" s="37">
-        <f>X110</f>
+        <f t="shared" si="50"/>
         <v>87</v>
       </c>
       <c r="Y212" s="37">
-        <f>Y110</f>
+        <f t="shared" si="50"/>
         <v>65</v>
       </c>
       <c r="Z212" s="37">
-        <f>Z110</f>
+        <f t="shared" si="50"/>
         <v>59</v>
       </c>
       <c r="AA212" s="37">
-        <f>AA110</f>
+        <f t="shared" si="50"/>
         <v>51</v>
       </c>
       <c r="AB212" s="37">
-        <f>AB110</f>
+        <f t="shared" si="50"/>
         <v>44</v>
       </c>
       <c r="AC212" s="37">
-        <f>AC110</f>
+        <f t="shared" si="50"/>
         <v>29</v>
       </c>
       <c r="AD212" s="37">
-        <f>AD110</f>
+        <f t="shared" si="50"/>
         <v>21</v>
       </c>
       <c r="AE212" s="37">
-        <f>AE110</f>
+        <f t="shared" si="50"/>
         <v>10</v>
       </c>
       <c r="AF212" s="37">
-        <f>AF110</f>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
     </row>
@@ -41006,112 +40980,145 @@
         <v>357</v>
       </c>
       <c r="G213" s="37">
-        <f t="shared" ref="G213:AF213" si="48">G207</f>
+        <f t="shared" ref="G213:AF213" si="51">G207</f>
         <v>347</v>
       </c>
       <c r="H213" s="37">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>335</v>
       </c>
       <c r="I213" s="37">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>322</v>
       </c>
       <c r="J213" s="37">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>310</v>
       </c>
       <c r="K213" s="37">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>308</v>
       </c>
       <c r="L213" s="37">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>267</v>
       </c>
       <c r="M213" s="37">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>269</v>
       </c>
       <c r="N213" s="37">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>228</v>
       </c>
       <c r="O213" s="37">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>227</v>
       </c>
       <c r="P213" s="37">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>224</v>
       </c>
       <c r="Q213" s="37">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>199</v>
       </c>
       <c r="R213" s="37">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>184</v>
       </c>
       <c r="S213" s="37">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>164</v>
       </c>
       <c r="T213" s="37">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>142</v>
       </c>
       <c r="U213" s="37">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>137</v>
       </c>
       <c r="V213" s="37">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>118</v>
       </c>
       <c r="W213" s="37">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>99</v>
       </c>
       <c r="X213" s="37">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>88</v>
       </c>
       <c r="Y213" s="37">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>70</v>
       </c>
       <c r="Z213" s="37">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>61</v>
       </c>
       <c r="AA213" s="37">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>55</v>
       </c>
       <c r="AB213" s="37">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>45</v>
       </c>
       <c r="AC213" s="37">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>27</v>
       </c>
       <c r="AD213" s="37">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>19</v>
       </c>
       <c r="AE213" s="37">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>8</v>
       </c>
       <c r="AF213" s="37">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:A35"/>
+    <mergeCell ref="A36:A50"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="A110:C110"/>
+    <mergeCell ref="A51:A65"/>
+    <mergeCell ref="A66:A79"/>
+    <mergeCell ref="A80:A93"/>
+    <mergeCell ref="A94:A107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="A114:B114"/>
+    <mergeCell ref="A115:B115"/>
+    <mergeCell ref="A116:B116"/>
+    <mergeCell ref="A117:B117"/>
+    <mergeCell ref="A118:A132"/>
     <mergeCell ref="A205:B205"/>
     <mergeCell ref="A206:B206"/>
     <mergeCell ref="A207:C207"/>
@@ -41121,39 +41128,6 @@
     <mergeCell ref="A163:A176"/>
     <mergeCell ref="A177:A190"/>
     <mergeCell ref="A191:A202"/>
-    <mergeCell ref="A114:B114"/>
-    <mergeCell ref="A115:B115"/>
-    <mergeCell ref="A116:B116"/>
-    <mergeCell ref="A117:B117"/>
-    <mergeCell ref="A118:A132"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="A110:C110"/>
-    <mergeCell ref="A51:A65"/>
-    <mergeCell ref="A66:A79"/>
-    <mergeCell ref="A80:A93"/>
-    <mergeCell ref="A94:A107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:A35"/>
-    <mergeCell ref="A36:A50"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="E13:G13"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="E11:G11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="B1:M1"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="K8:L8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -41178,42 +41152,42 @@
   </cols>
   <sheetData>
     <row r="2" spans="5:15" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="E2" s="104" t="s">
+      <c r="E2" s="122" t="s">
         <v>104</v>
       </c>
-      <c r="F2" s="105"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="105"/>
-      <c r="I2" s="105"/>
-      <c r="J2" s="105"/>
-      <c r="K2" s="105"/>
-      <c r="L2" s="105"/>
-      <c r="M2" s="105"/>
-      <c r="N2" s="105"/>
-      <c r="O2" s="105"/>
+      <c r="F2" s="123"/>
+      <c r="G2" s="123"/>
+      <c r="H2" s="123"/>
+      <c r="I2" s="123"/>
+      <c r="J2" s="123"/>
+      <c r="K2" s="123"/>
+      <c r="L2" s="123"/>
+      <c r="M2" s="123"/>
+      <c r="N2" s="123"/>
+      <c r="O2" s="123"/>
     </row>
     <row r="3" spans="5:15" ht="16.8" x14ac:dyDescent="0.3">
       <c r="E3" s="93"/>
-      <c r="F3" s="106" t="s">
+      <c r="F3" s="124" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="107"/>
-      <c r="H3" s="106" t="s">
+      <c r="G3" s="125"/>
+      <c r="H3" s="124" t="s">
         <v>42</v>
       </c>
-      <c r="I3" s="107"/>
-      <c r="J3" s="106" t="s">
+      <c r="I3" s="125"/>
+      <c r="J3" s="124" t="s">
         <v>46</v>
       </c>
-      <c r="K3" s="107"/>
-      <c r="L3" s="106" t="s">
+      <c r="K3" s="125"/>
+      <c r="L3" s="124" t="s">
         <v>40</v>
       </c>
-      <c r="M3" s="107"/>
-      <c r="N3" s="106" t="s">
+      <c r="M3" s="125"/>
+      <c r="N3" s="124" t="s">
         <v>44</v>
       </c>
-      <c r="O3" s="107"/>
+      <c r="O3" s="125"/>
     </row>
     <row r="4" spans="5:15" ht="33.6" x14ac:dyDescent="0.3">
       <c r="E4" s="24"/>
@@ -41364,10 +41338,10 @@
       </c>
     </row>
     <row r="11" spans="5:15" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="H11" s="103" t="s">
+      <c r="H11" s="121" t="s">
         <v>106</v>
       </c>
-      <c r="I11" s="103"/>
+      <c r="I11" s="121"/>
     </row>
     <row r="12" spans="5:15" ht="16.8" x14ac:dyDescent="0.3">
       <c r="H12" s="100" t="s">
